--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ50"/>
+  <dimension ref="A1:AI50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="2" customWidth="1" min="13" max="13"/>
+    <col width="2" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
@@ -517,12 +517,11 @@
     <col width="25" customWidth="1" min="28" max="28"/>
     <col width="25" customWidth="1" min="29" max="29"/>
     <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="25" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="2" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="2" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
     <col width="15" customWidth="1" min="35" max="35"/>
-    <col width="15" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -544,12 +543,12 @@
       <c r="I1" s="4" t="n"/>
       <c r="J1" s="4" t="n"/>
       <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Molar extinction coefficients in MeCN / mM-1 cm-1</t>
         </is>
       </c>
+      <c r="N1" s="6" t="n"/>
       <c r="O1" s="6" t="n"/>
       <c r="P1" s="6" t="n"/>
       <c r="Q1" s="6" t="n"/>
@@ -567,14 +566,13 @@
       <c r="AC1" s="6" t="n"/>
       <c r="AD1" s="6" t="n"/>
       <c r="AE1" s="6" t="n"/>
-      <c r="AF1" s="6" t="n"/>
-      <c r="AH1" s="7" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>Sample</t>
         </is>
       </c>
+      <c r="AH1" s="8" t="n"/>
       <c r="AI1" s="8" t="n"/>
-      <c r="AJ1" s="8" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -619,125 +617,120 @@
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>redox_source_type</t>
+          <t>source</t>
         </is>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>redox_source_note</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>redox_doi</t>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>epsilon_380 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_380 / mM-1 cm-1</t>
+          <t>epsilon_390 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_390 / mM-1 cm-1</t>
+          <t>epsilon_400 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_400 / mM-1 cm-1</t>
+          <t>epsilon_405 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="Q2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_405 / mM-1 cm-1</t>
+          <t>epsilon_415 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="R2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_415 / mM-1 cm-1</t>
+          <t>epsilon_425 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="S2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_425 / mM-1 cm-1</t>
+          <t>epsilon_450 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="T2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_450 / mM-1 cm-1</t>
+          <t>epsilon_475 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="U2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_475 / mM-1 cm-1</t>
+          <t>epsilon_490 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="V2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_490 / mM-1 cm-1</t>
+          <t>epsilon_495 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="W2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_495 / mM-1 cm-1</t>
+          <t>epsilon_500 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="X2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_500 / mM-1 cm-1</t>
+          <t>epsilon_510 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="Y2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_510 / mM-1 cm-1</t>
+          <t>epsilon_520 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="Z2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_520 / mM-1 cm-1</t>
+          <t>epsilon_580 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="AA2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_580 / mM-1 cm-1</t>
+          <t>epsilon_590 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="AB2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_590 / mM-1 cm-1</t>
+          <t>epsilon_600 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="AC2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_600 / mM-1 cm-1</t>
+          <t>epsilon_625 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="AD2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_625 / mM-1 cm-1</t>
+          <t>epsilon_645 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="AE2" s="11" t="inlineStr">
         <is>
-          <t>epsilon_645 / mM-1 cm-1</t>
-        </is>
-      </c>
-      <c r="AF2" s="11" t="inlineStr">
-        <is>
           <t>max_read_rsd / %</t>
         </is>
       </c>
+      <c r="AG2" s="12" t="inlineStr">
+        <is>
+          <t>c_stock / mM</t>
+        </is>
+      </c>
       <c r="AH2" s="12" t="inlineStr">
         <is>
-          <t>c_stock / mM</t>
+          <t>deck_position</t>
         </is>
       </c>
       <c r="AI2" s="12" t="inlineStr">
-        <is>
-          <t>deck_position</t>
-        </is>
-      </c>
-      <c r="AJ2" s="12" t="inlineStr">
         <is>
           <t>well_position</t>
         </is>
@@ -780,7 +773,7 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
@@ -788,73 +781,72 @@
           <t>measured by PPR</t>
         </is>
       </c>
-      <c r="L3" s="13" t="n"/>
+      <c r="M3" s="13" t="n">
+        <v>0.0038773</v>
+      </c>
       <c r="N3" s="13" t="n">
-        <v>0.0038773</v>
+        <v>0.00364922</v>
       </c>
       <c r="O3" s="13" t="n">
-        <v>0.00364922</v>
+        <v>0.00340689</v>
       </c>
       <c r="P3" s="13" t="n">
-        <v>0.00340689</v>
+        <v>0.0033071</v>
       </c>
       <c r="Q3" s="13" t="n">
-        <v>0.0033071</v>
+        <v>0.00307903</v>
       </c>
       <c r="R3" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.00297925</v>
       </c>
       <c r="S3" s="13" t="n">
-        <v>0.00297925</v>
+        <v>0.00273691</v>
       </c>
       <c r="T3" s="13" t="n">
-        <v>0.00273691</v>
+        <v>0.00245182</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>0.00245182</v>
+        <v>0.00243756</v>
       </c>
       <c r="V3" s="13" t="n">
-        <v>0.00243756</v>
+        <v>0.00232353</v>
       </c>
       <c r="W3" s="13" t="n">
-        <v>0.00232353</v>
+        <v>0.0023948</v>
       </c>
       <c r="X3" s="13" t="n">
-        <v>0.0023948</v>
+        <v>0.00246607</v>
       </c>
       <c r="Y3" s="13" t="n">
         <v>0.00246607</v>
       </c>
       <c r="Z3" s="13" t="n">
-        <v>0.00246607</v>
+        <v>0.00229502</v>
       </c>
       <c r="AA3" s="13" t="n">
-        <v>0.00229502</v>
+        <v>0.00235204</v>
       </c>
       <c r="AB3" s="13" t="n">
-        <v>0.00235204</v>
+        <v>0.00219523</v>
       </c>
       <c r="AC3" s="13" t="n">
-        <v>0.00219523</v>
+        <v>0.00222374</v>
       </c>
       <c r="AD3" s="13" t="n">
-        <v>0.00222374</v>
+        <v>0.00233778</v>
       </c>
       <c r="AE3" s="13" t="n">
-        <v>0.00233778</v>
-      </c>
-      <c r="AF3" s="13" t="n">
         <v>5.39127</v>
       </c>
-      <c r="AH3" s="13" t="n">
+      <c r="AG3" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH3" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI3" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ3" s="13" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -889,7 +881,7 @@
       <c r="I4" s="13" t="n"/>
       <c r="J4" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1002/chem.201901175</t>
         </is>
       </c>
       <c r="K4" s="13" t="inlineStr">
@@ -897,77 +889,72 @@
           <t>in MeCN</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>https://chemistry-europe.onlinelibrary.wiley.com/action/downloadSupplement?doi=10.1002%2Fchem.201901175&amp;file=chem201901175-sup-0001-misc_information.pdf</t>
-        </is>
+      <c r="M4" s="13" t="n">
+        <v>0.00285095</v>
       </c>
       <c r="N4" s="13" t="n">
         <v>0.00285095</v>
       </c>
       <c r="O4" s="13" t="n">
-        <v>0.00285095</v>
+        <v>0.0028367</v>
       </c>
       <c r="P4" s="13" t="n">
-        <v>0.0028367</v>
+        <v>0.00262288</v>
       </c>
       <c r="Q4" s="13" t="n">
         <v>0.00262288</v>
       </c>
       <c r="R4" s="13" t="n">
-        <v>0.00262288</v>
+        <v>0.00240905</v>
       </c>
       <c r="S4" s="13" t="n">
-        <v>0.00240905</v>
+        <v>0.00216672</v>
       </c>
       <c r="T4" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.0021097</v>
       </c>
       <c r="U4" s="13" t="n">
-        <v>0.0021097</v>
+        <v>0.00198141</v>
       </c>
       <c r="V4" s="13" t="n">
-        <v>0.00198141</v>
+        <v>0.00186737</v>
       </c>
       <c r="W4" s="13" t="n">
-        <v>0.00186737</v>
+        <v>0.00193865</v>
       </c>
       <c r="X4" s="13" t="n">
-        <v>0.00193865</v>
+        <v>0.00200992</v>
       </c>
       <c r="Y4" s="13" t="n">
-        <v>0.00200992</v>
+        <v>0.00189588</v>
       </c>
       <c r="Z4" s="13" t="n">
-        <v>0.00189588</v>
+        <v>0.00161079</v>
       </c>
       <c r="AA4" s="13" t="n">
-        <v>0.00161079</v>
+        <v>0.00178185</v>
       </c>
       <c r="AB4" s="13" t="n">
-        <v>0.00178185</v>
+        <v>0.001511</v>
       </c>
       <c r="AC4" s="13" t="n">
-        <v>0.001511</v>
+        <v>0.00153951</v>
       </c>
       <c r="AD4" s="13" t="n">
         <v>0.00153951</v>
       </c>
       <c r="AE4" s="13" t="n">
-        <v>0.00153951</v>
-      </c>
-      <c r="AF4" s="13" t="n">
         <v>6.45161</v>
       </c>
-      <c r="AH4" s="13" t="n">
+      <c r="AG4" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH4" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI4" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ4" s="13" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
@@ -1000,85 +987,80 @@
       <c r="I5" s="13" t="n"/>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1016/j.jelechem.2003.09.011</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>converted from FC/FC+ to SCE</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0022072803005448?via%3Dihub</t>
-        </is>
+          <t>converted from Fc/Fc+ to SCE</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>0.112213</v>
       </c>
       <c r="N5" s="13" t="n">
-        <v>0.112213</v>
+        <v>0.0586156</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0.0586156</v>
+        <v>0.0232495</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>0.0232495</v>
+        <v>0.0117459</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>0.0117459</v>
+        <v>0.00376326</v>
       </c>
       <c r="R5" s="13" t="n">
-        <v>0.00376326</v>
+        <v>0.00229502</v>
       </c>
       <c r="S5" s="13" t="n">
-        <v>0.00229502</v>
+        <v>0.00205269</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>0.00205269</v>
+        <v>0.00188163</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>0.00188163</v>
+        <v>0.00186737</v>
       </c>
       <c r="V5" s="13" t="n">
-        <v>0.00186737</v>
+        <v>0.00175334</v>
       </c>
       <c r="W5" s="13" t="n">
-        <v>0.00175334</v>
+        <v>0.00182461</v>
       </c>
       <c r="X5" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00200992</v>
       </c>
       <c r="Y5" s="13" t="n">
-        <v>0.00200992</v>
+        <v>0.00178185</v>
       </c>
       <c r="Z5" s="13" t="n">
+        <v>0.00172483</v>
+      </c>
+      <c r="AA5" s="13" t="n">
         <v>0.00178185</v>
       </c>
-      <c r="AA5" s="13" t="n">
-        <v>0.00172483</v>
-      </c>
       <c r="AB5" s="13" t="n">
-        <v>0.00178185</v>
+        <v>0.00162504</v>
       </c>
       <c r="AC5" s="13" t="n">
-        <v>0.00162504</v>
+        <v>0.00165355</v>
       </c>
       <c r="AD5" s="13" t="n">
-        <v>0.00165355</v>
+        <v>0.00176759</v>
       </c>
       <c r="AE5" s="13" t="n">
-        <v>0.00176759</v>
-      </c>
-      <c r="AF5" s="13" t="n">
         <v>5.80073</v>
       </c>
-      <c r="AH5" s="13" t="n">
+      <c r="AG5" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH5" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI5" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ5" s="13" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
@@ -1117,81 +1099,76 @@
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1016/j.chempr.2019.06.004</t>
         </is>
       </c>
       <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>https://www.cell.com/chem/fulltext/S2451-9294(19)30266-9</t>
-        </is>
+      <c r="M6" s="13" t="n">
+        <v>0.00319307</v>
       </c>
       <c r="N6" s="13" t="n">
         <v>0.00319307</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0.00319307</v>
+        <v>0.00306477</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>0.00306477</v>
+        <v>0.00296499</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.00296499</v>
+        <v>0.00262288</v>
       </c>
       <c r="R6" s="13" t="n">
-        <v>0.00262288</v>
+        <v>0.00263713</v>
       </c>
       <c r="S6" s="13" t="n">
-        <v>0.00263713</v>
+        <v>0.00228076</v>
       </c>
       <c r="T6" s="13" t="n">
-        <v>0.00228076</v>
+        <v>0.00199567</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>0.00199567</v>
+        <v>0.00209545</v>
       </c>
       <c r="V6" s="13" t="n">
         <v>0.00209545</v>
       </c>
       <c r="W6" s="13" t="n">
-        <v>0.00209545</v>
+        <v>0.00193865</v>
       </c>
       <c r="X6" s="13" t="n">
-        <v>0.00193865</v>
+        <v>0.00200992</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>0.00200992</v>
+        <v>0.00189588</v>
       </c>
       <c r="Z6" s="13" t="n">
-        <v>0.00189588</v>
+        <v>0.00149675</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>0.00149675</v>
+        <v>0.00155377</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>0.00155377</v>
+        <v>0.00128293</v>
       </c>
       <c r="AC6" s="13" t="n">
-        <v>0.00128293</v>
+        <v>0.00142548</v>
       </c>
       <c r="AD6" s="13" t="n">
         <v>0.00142548</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>0.00142548</v>
-      </c>
-      <c r="AF6" s="13" t="n">
         <v>6.19267</v>
       </c>
-      <c r="AH6" s="13" t="n">
+      <c r="AG6" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH6" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI6" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ6" s="13" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
@@ -1224,81 +1201,76 @@
       <c r="I7" s="13" t="n"/>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1039/j19680000381</t>
         </is>
       </c>
       <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>https://pubs.rsc.org/en/content/articlepdf/1968/j1/j19680000381</t>
-        </is>
+      <c r="M7" s="13" t="n">
+        <v>0.0226936</v>
       </c>
       <c r="N7" s="13" t="n">
-        <v>0.0226936</v>
+        <v>0.00695632</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>0.00695632</v>
+        <v>0.0052315</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>0.0052315</v>
+        <v>0.00467556</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.00467556</v>
+        <v>0.00433345</v>
       </c>
       <c r="R7" s="13" t="n">
-        <v>0.00433345</v>
+        <v>0.00389155</v>
       </c>
       <c r="S7" s="13" t="n">
-        <v>0.00389155</v>
+        <v>0.00319307</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>0.00319307</v>
+        <v>0.00279393</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>0.00279393</v>
+        <v>0.0025516</v>
       </c>
       <c r="V7" s="13" t="n">
         <v>0.0025516</v>
       </c>
       <c r="W7" s="13" t="n">
-        <v>0.0025516</v>
+        <v>0.0023948</v>
       </c>
       <c r="X7" s="13" t="n">
-        <v>0.0023948</v>
+        <v>0.00235204</v>
       </c>
       <c r="Y7" s="13" t="n">
         <v>0.00235204</v>
       </c>
       <c r="Z7" s="13" t="n">
-        <v>0.00235204</v>
+        <v>0.00172483</v>
       </c>
       <c r="AA7" s="13" t="n">
-        <v>0.00172483</v>
+        <v>0.00178185</v>
       </c>
       <c r="AB7" s="13" t="n">
-        <v>0.00178185</v>
+        <v>0.001511</v>
       </c>
       <c r="AC7" s="13" t="n">
-        <v>0.001511</v>
+        <v>0.00153951</v>
       </c>
       <c r="AD7" s="13" t="n">
         <v>0.00153951</v>
       </c>
       <c r="AE7" s="13" t="n">
-        <v>0.00153951</v>
-      </c>
-      <c r="AF7" s="13" t="n">
         <v>6.19267</v>
       </c>
-      <c r="AH7" s="13" t="n">
+      <c r="AG7" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH7" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI7" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ7" s="13" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
@@ -1331,81 +1303,76 @@
       <c r="I8" s="13" t="n"/>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1039/j19680000381</t>
         </is>
       </c>
       <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>https://pubs.rsc.org/en/content/articlepdf/1968/j1/j19680000381</t>
-        </is>
+      <c r="M8" s="13" t="n">
+        <v>0.0102634</v>
       </c>
       <c r="N8" s="13" t="n">
-        <v>0.0102634</v>
+        <v>0.00923709</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>0.00923709</v>
+        <v>0.008424559999999999</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>0.008424559999999999</v>
+        <v>0.0080967</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.0080967</v>
+        <v>0.00741248</v>
       </c>
       <c r="R8" s="13" t="n">
-        <v>0.00741248</v>
+        <v>0.00685654</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>0.00685654</v>
+        <v>0.00524575</v>
       </c>
       <c r="T8" s="13" t="n">
-        <v>0.00524575</v>
+        <v>0.00461854</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>0.00461854</v>
+        <v>0.00437621</v>
       </c>
       <c r="V8" s="13" t="n">
-        <v>0.00437621</v>
+        <v>0.00426217</v>
       </c>
       <c r="W8" s="13" t="n">
-        <v>0.00426217</v>
+        <v>0.00421941</v>
       </c>
       <c r="X8" s="13" t="n">
-        <v>0.00421941</v>
+        <v>0.00406261</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>0.00406261</v>
+        <v>0.00417664</v>
       </c>
       <c r="Z8" s="13" t="n">
-        <v>0.00417664</v>
+        <v>0.00354944</v>
       </c>
       <c r="AA8" s="13" t="n">
-        <v>0.00354944</v>
+        <v>0.00349242</v>
       </c>
       <c r="AB8" s="13" t="n">
-        <v>0.00349242</v>
+        <v>0.00333561</v>
       </c>
       <c r="AC8" s="13" t="n">
-        <v>0.00333561</v>
+        <v>0.00325009</v>
       </c>
       <c r="AD8" s="13" t="n">
         <v>0.00325009</v>
       </c>
       <c r="AE8" s="13" t="n">
-        <v>0.00325009</v>
-      </c>
-      <c r="AF8" s="13" t="n">
         <v>6.18317</v>
       </c>
-      <c r="AH8" s="13" t="n">
+      <c r="AG8" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH8" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI8" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ8" s="13" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -1444,7 +1411,7 @@
       <c r="I9" s="13" t="n"/>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1038/s41586-022-04636-x</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -1452,77 +1419,72 @@
           <t>in MeCN</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>Intermolecular [2π+2σ]-photocycloaddition enabled by triplet energy transfer | Nature</t>
-        </is>
+      <c r="M9" s="13" t="n">
+        <v>0.00410537</v>
       </c>
       <c r="N9" s="13" t="n">
-        <v>0.00410537</v>
+        <v>0.00376326</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>0.00376326</v>
+        <v>0.00363496</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>0.00363496</v>
+        <v>0.0033071</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.0033071</v>
+        <v>0.00307903</v>
       </c>
       <c r="R9" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.00286521</v>
       </c>
       <c r="S9" s="13" t="n">
-        <v>0.00286521</v>
+        <v>0.00262288</v>
       </c>
       <c r="T9" s="13" t="n">
-        <v>0.00262288</v>
+        <v>0.00233778</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>0.00233778</v>
+        <v>0.00243756</v>
       </c>
       <c r="V9" s="13" t="n">
-        <v>0.00243756</v>
+        <v>0.00220949</v>
       </c>
       <c r="W9" s="13" t="n">
-        <v>0.00220949</v>
+        <v>0.00228076</v>
       </c>
       <c r="X9" s="13" t="n">
-        <v>0.00228076</v>
+        <v>0.00212396</v>
       </c>
       <c r="Y9" s="13" t="n">
-        <v>0.00212396</v>
+        <v>0.002238</v>
       </c>
       <c r="Z9" s="13" t="n">
-        <v>0.002238</v>
+        <v>0.00183886</v>
       </c>
       <c r="AA9" s="13" t="n">
-        <v>0.00183886</v>
+        <v>0.00200992</v>
       </c>
       <c r="AB9" s="13" t="n">
-        <v>0.00200992</v>
+        <v>0.00185312</v>
       </c>
       <c r="AC9" s="13" t="n">
-        <v>0.00185312</v>
+        <v>0.00165355</v>
       </c>
       <c r="AD9" s="13" t="n">
-        <v>0.00165355</v>
+        <v>0.00176759</v>
       </c>
       <c r="AE9" s="13" t="n">
-        <v>0.00176759</v>
-      </c>
-      <c r="AF9" s="13" t="n">
         <v>6.0297</v>
       </c>
-      <c r="AH9" s="13" t="n">
+      <c r="AG9" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH9" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI9" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ9" s="13" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
@@ -1561,85 +1523,80 @@
       <c r="I10" s="13" t="n"/>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>https://doi.org/10.1038/s41557-022-01008-w</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>similar bifunctional with Me instead of iPr</t>
-        </is>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>Photochemical single-step synthesis of β-amino acid derivatives from alkenes and (hetero)arenes | Nature Chemistry</t>
-        </is>
+          <t>estimated: the value is for the analog with Me instead of iPr</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.00399133</v>
       </c>
       <c r="N10" s="13" t="n">
-        <v>0.00399133</v>
+        <v>0.00376326</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.00376326</v>
+        <v>0.00363496</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>0.00363496</v>
+        <v>0.00353518</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.00353518</v>
+        <v>0.00342114</v>
       </c>
       <c r="R10" s="13" t="n">
-        <v>0.00342114</v>
+        <v>0.00320732</v>
       </c>
       <c r="S10" s="13" t="n">
-        <v>0.00320732</v>
+        <v>0.00285095</v>
       </c>
       <c r="T10" s="13" t="n">
-        <v>0.00285095</v>
+        <v>0.0026799</v>
       </c>
       <c r="U10" s="13" t="n">
-        <v>0.0026799</v>
+        <v>0.00266564</v>
       </c>
       <c r="V10" s="13" t="n">
         <v>0.00266564</v>
       </c>
       <c r="W10" s="13" t="n">
-        <v>0.00266564</v>
+        <v>0.00262288</v>
       </c>
       <c r="X10" s="13" t="n">
-        <v>0.00262288</v>
+        <v>0.00246607</v>
       </c>
       <c r="Y10" s="13" t="n">
-        <v>0.00246607</v>
+        <v>0.00258011</v>
       </c>
       <c r="Z10" s="13" t="n">
-        <v>0.00258011</v>
+        <v>0.00206694</v>
       </c>
       <c r="AA10" s="13" t="n">
-        <v>0.00206694</v>
+        <v>0.002238</v>
       </c>
       <c r="AB10" s="13" t="n">
-        <v>0.002238</v>
+        <v>0.00196716</v>
       </c>
       <c r="AC10" s="13" t="n">
-        <v>0.00196716</v>
+        <v>0.00199567</v>
       </c>
       <c r="AD10" s="13" t="n">
         <v>0.00199567</v>
       </c>
       <c r="AE10" s="13" t="n">
-        <v>0.00199567</v>
-      </c>
-      <c r="AF10" s="13" t="n">
         <v>4.58258</v>
       </c>
-      <c r="AH10" s="13" t="n">
+      <c r="AG10" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH10" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI10" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ10" s="13" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
@@ -1678,77 +1635,80 @@
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>unattributed</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>no lab record; consistent with the deposited voltammogram (009)</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.00296499</v>
+      </c>
       <c r="N11" s="13" t="n">
-        <v>0.00296499</v>
+        <v>0.00285095</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0.00285095</v>
+        <v>0.00272266</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>0.00272266</v>
+        <v>0.00262288</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.00262288</v>
+        <v>0.0023948</v>
       </c>
       <c r="R11" s="13" t="n">
-        <v>0.0023948</v>
+        <v>0.00240905</v>
       </c>
       <c r="S11" s="13" t="n">
-        <v>0.00240905</v>
+        <v>0.00216672</v>
       </c>
       <c r="T11" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.0021097</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>0.0021097</v>
+        <v>0.00209545</v>
       </c>
       <c r="V11" s="13" t="n">
-        <v>0.00209545</v>
+        <v>0.00198141</v>
       </c>
       <c r="W11" s="13" t="n">
-        <v>0.00198141</v>
+        <v>0.00205269</v>
       </c>
       <c r="X11" s="13" t="n">
-        <v>0.00205269</v>
+        <v>0.00200992</v>
       </c>
       <c r="Y11" s="13" t="n">
         <v>0.00200992</v>
       </c>
       <c r="Z11" s="13" t="n">
-        <v>0.00200992</v>
+        <v>0.0019529</v>
       </c>
       <c r="AA11" s="13" t="n">
-        <v>0.0019529</v>
+        <v>0.00212396</v>
       </c>
       <c r="AB11" s="13" t="n">
-        <v>0.00212396</v>
+        <v>0.00185312</v>
       </c>
       <c r="AC11" s="13" t="n">
-        <v>0.00185312</v>
+        <v>0.00199567</v>
       </c>
       <c r="AD11" s="13" t="n">
-        <v>0.00199567</v>
+        <v>0.00222374</v>
       </c>
       <c r="AE11" s="13" t="n">
-        <v>0.00222374</v>
-      </c>
-      <c r="AF11" s="13" t="n">
         <v>6.66173</v>
       </c>
-      <c r="AH11" s="13" t="n">
+      <c r="AG11" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH11" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI11" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ11" s="13" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
@@ -1783,85 +1743,80 @@
       <c r="I12" s="13" t="n"/>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1016/j.electacta.2005.02.033; https://doi.org/10.1080/08843759008915951</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0013468605002264</t>
-        </is>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>https://www.tandfonline.com/doi/epdf/10.1080/08843759008915951?needAccess=true</t>
-        </is>
+          <t>two references recorded, not assigned to E_Ox or E_Red</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0195005</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>0.0195005</v>
+        <v>0.00980728</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.00980728</v>
+        <v>0.00545957</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>0.00545957</v>
+        <v>0.00410537</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.00410537</v>
+        <v>0.00273691</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>0.00273691</v>
+        <v>0.00206694</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>0.00206694</v>
+        <v>0.0014825</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>0.0014825</v>
+        <v>0.00142548</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>0.00142548</v>
+        <v>0.00129718</v>
       </c>
       <c r="V12" s="13" t="n">
         <v>0.00129718</v>
       </c>
       <c r="W12" s="13" t="n">
-        <v>0.00129718</v>
+        <v>0.0014825</v>
       </c>
       <c r="X12" s="13" t="n">
-        <v>0.0014825</v>
+        <v>0.00155377</v>
       </c>
       <c r="Y12" s="13" t="n">
-        <v>0.00155377</v>
+        <v>0.00132569</v>
       </c>
       <c r="Z12" s="13" t="n">
+        <v>0.00115464</v>
+      </c>
+      <c r="AA12" s="13" t="n">
         <v>0.00132569</v>
       </c>
-      <c r="AA12" s="13" t="n">
-        <v>0.00115464</v>
-      </c>
       <c r="AB12" s="13" t="n">
-        <v>0.00132569</v>
+        <v>0.00116889</v>
       </c>
       <c r="AC12" s="13" t="n">
-        <v>0.00116889</v>
+        <v>0.0011974</v>
       </c>
       <c r="AD12" s="13" t="n">
-        <v>0.0011974</v>
+        <v>0.00142548</v>
       </c>
       <c r="AE12" s="13" t="n">
-        <v>0.00142548</v>
-      </c>
-      <c r="AF12" s="13" t="n">
         <v>6.2775</v>
       </c>
-      <c r="AH12" s="13" t="n">
+      <c r="AG12" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH12" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI12" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ12" s="13" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
@@ -1896,85 +1851,80 @@
       <c r="I13" s="13" t="n"/>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1016/j.electacta.2005.02.033; https://doi.org/10.1080/08843759008915951</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0013468605002264</t>
-        </is>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>https://www.tandfonline.com/doi/epdf/10.1080/08843759008915951?needAccess=true</t>
-        </is>
+          <t>two references recorded, not assigned to E_Ox or E_Red</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.00250884</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>0.00250884</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>0.00250884</v>
+        <v>0.00238055</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>0.00238055</v>
+        <v>0.00228076</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.00228076</v>
+        <v>0.00216672</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.00206694</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>0.00206694</v>
+        <v>0.00182461</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00153951</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>0.00153951</v>
+        <v>0.0016393</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>0.0016393</v>
+        <v>0.00152526</v>
       </c>
       <c r="W13" s="13" t="n">
-        <v>0.00152526</v>
+        <v>0.00159653</v>
       </c>
       <c r="X13" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.00155377</v>
       </c>
       <c r="Y13" s="13" t="n">
         <v>0.00155377</v>
       </c>
       <c r="Z13" s="13" t="n">
-        <v>0.00155377</v>
+        <v>0.00126867</v>
       </c>
       <c r="AA13" s="13" t="n">
-        <v>0.00126867</v>
+        <v>0.00143973</v>
       </c>
       <c r="AB13" s="13" t="n">
-        <v>0.00143973</v>
+        <v>0.00116889</v>
       </c>
       <c r="AC13" s="13" t="n">
-        <v>0.00116889</v>
+        <v>0.0011974</v>
       </c>
       <c r="AD13" s="13" t="n">
         <v>0.0011974</v>
       </c>
       <c r="AE13" s="13" t="n">
-        <v>0.0011974</v>
-      </c>
-      <c r="AF13" s="13" t="n">
         <v>7.87296</v>
       </c>
-      <c r="AH13" s="13" t="n">
+      <c r="AG13" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH13" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI13" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ13" s="13" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
@@ -2013,81 +1963,76 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L14" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n"/>
+      <c r="M14" s="13" t="n">
+        <v>0.00296499</v>
+      </c>
       <c r="N14" s="13" t="n">
-        <v>0.00296499</v>
+        <v>0.00250884</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>0.00250884</v>
+        <v>0.00226651</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>0.00226651</v>
+        <v>0.00216672</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.00182461</v>
       </c>
       <c r="R14" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00172483</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>0.00172483</v>
+        <v>0.0014825</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>0.0014825</v>
+        <v>0.00142548</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>0.00142548</v>
+        <v>0.00129718</v>
       </c>
       <c r="V14" s="13" t="n">
         <v>0.00129718</v>
       </c>
       <c r="W14" s="13" t="n">
-        <v>0.00129718</v>
+        <v>0.00125442</v>
       </c>
       <c r="X14" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.00121165</v>
       </c>
       <c r="Y14" s="13" t="n">
-        <v>0.00121165</v>
+        <v>0.00132569</v>
       </c>
       <c r="Z14" s="13" t="n">
-        <v>0.00132569</v>
+        <v>0.000926559</v>
       </c>
       <c r="AA14" s="13" t="n">
-        <v>0.000926559</v>
+        <v>0.00109762</v>
       </c>
       <c r="AB14" s="13" t="n">
-        <v>0.00109762</v>
+        <v>0.000826776</v>
       </c>
       <c r="AC14" s="13" t="n">
-        <v>0.000826776</v>
+        <v>0.000969324</v>
       </c>
       <c r="AD14" s="13" t="n">
         <v>0.000969324</v>
       </c>
       <c r="AE14" s="13" t="n">
-        <v>0.000969324</v>
-      </c>
-      <c r="AF14" s="13" t="n">
         <v>7.87296</v>
       </c>
-      <c r="AH14" s="13" t="n">
+      <c r="AG14" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH14" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI14" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ14" s="13" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
@@ -2120,81 +2065,76 @@
       <c r="I15" s="13" t="n"/>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1016/S0040-4039(00)01248-X</t>
         </is>
       </c>
       <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S004040390001248X</t>
-        </is>
+      <c r="M15" s="13" t="n">
+        <v>0.0047896</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>0.0047896</v>
+        <v>0.00307903</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.00272266</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>0.00272266</v>
+        <v>0.00250884</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.00250884</v>
+        <v>0.00216672</v>
       </c>
       <c r="R15" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.00206694</v>
       </c>
       <c r="S15" s="13" t="n">
-        <v>0.00206694</v>
+        <v>0.00182461</v>
       </c>
       <c r="T15" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00176759</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>0.00176759</v>
+        <v>0.00175334</v>
       </c>
       <c r="V15" s="13" t="n">
-        <v>0.00175334</v>
+        <v>0.0016393</v>
       </c>
       <c r="W15" s="13" t="n">
-        <v>0.0016393</v>
+        <v>0.00159653</v>
       </c>
       <c r="X15" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.00155377</v>
       </c>
       <c r="Y15" s="13" t="n">
-        <v>0.00155377</v>
+        <v>0.00166781</v>
       </c>
       <c r="Z15" s="13" t="n">
-        <v>0.00166781</v>
+        <v>0.00126867</v>
       </c>
       <c r="AA15" s="13" t="n">
-        <v>0.00126867</v>
+        <v>0.00132569</v>
       </c>
       <c r="AB15" s="13" t="n">
-        <v>0.00132569</v>
+        <v>0.00116889</v>
       </c>
       <c r="AC15" s="13" t="n">
-        <v>0.00116889</v>
+        <v>0.00108336</v>
       </c>
       <c r="AD15" s="13" t="n">
         <v>0.00108336</v>
       </c>
       <c r="AE15" s="13" t="n">
-        <v>0.00108336</v>
-      </c>
-      <c r="AF15" s="13" t="n">
         <v>4.94872</v>
       </c>
-      <c r="AH15" s="13" t="n">
+      <c r="AG15" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH15" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI15" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ15" s="13" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
@@ -2227,81 +2167,76 @@
       <c r="I16" s="13" t="n"/>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
           <t>https://doi.org/10.1246/bcsj.51.339</t>
         </is>
       </c>
-      <c r="L16" s="13" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="M16" s="13" t="n">
+        <v>0.00216672</v>
+      </c>
       <c r="N16" s="13" t="n">
         <v>0.00216672</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.00215247</v>
       </c>
       <c r="P16" s="13" t="n">
-        <v>0.00215247</v>
+        <v>0.00205269</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.00205269</v>
+        <v>0.00193865</v>
       </c>
       <c r="R16" s="13" t="n">
-        <v>0.00193865</v>
+        <v>0.0019529</v>
       </c>
       <c r="S16" s="13" t="n">
-        <v>0.0019529</v>
+        <v>0.00171057</v>
       </c>
       <c r="T16" s="13" t="n">
-        <v>0.00171057</v>
+        <v>0.00153951</v>
       </c>
       <c r="U16" s="13" t="n">
-        <v>0.00153951</v>
+        <v>0.0016393</v>
       </c>
       <c r="V16" s="13" t="n">
-        <v>0.0016393</v>
+        <v>0.00141122</v>
       </c>
       <c r="W16" s="13" t="n">
-        <v>0.00141122</v>
+        <v>0.0014825</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>0.0014825</v>
+        <v>0.00155377</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>0.00155377</v>
+        <v>0.00143973</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>0.00143973</v>
+        <v>0.00115464</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>0.00115464</v>
+        <v>0.00121165</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>0.00121165</v>
+        <v>0.00116889</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>0.00116889</v>
+        <v>0.0011974</v>
       </c>
       <c r="AD16" s="13" t="n">
         <v>0.0011974</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>0.0011974</v>
-      </c>
-      <c r="AF16" s="13" t="n">
         <v>9.123279999999999</v>
       </c>
-      <c r="AH16" s="13" t="n">
+      <c r="AG16" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH16" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI16" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ16" s="13" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
@@ -2334,85 +2269,80 @@
       <c r="I17" s="13" t="n"/>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1038/s41929-023-01089-x</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>Reduction potential not mentioned</t>
-        </is>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>Ring expansion of indene by photoredox-enabled functionalized carbon-atom insertion | Nature Catalysis</t>
-        </is>
+          <t>reduction potential not reported</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.00319307</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>0.00319307</v>
+        <v>0.00296499</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>0.00296499</v>
+        <v>0.0028367</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>0.0028367</v>
+        <v>0.00262288</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.00262288</v>
+        <v>0.00250884</v>
       </c>
       <c r="R17" s="13" t="n">
-        <v>0.00250884</v>
+        <v>0.00240905</v>
       </c>
       <c r="S17" s="13" t="n">
-        <v>0.00240905</v>
+        <v>0.00216672</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.00188163</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>0.00188163</v>
+        <v>0.00198141</v>
       </c>
       <c r="V17" s="13" t="n">
-        <v>0.00198141</v>
+        <v>0.00175334</v>
       </c>
       <c r="W17" s="13" t="n">
-        <v>0.00175334</v>
+        <v>0.00182461</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00189588</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>0.00189588</v>
+        <v>0.00178185</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>0.00178185</v>
+        <v>0.00149675</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>0.00149675</v>
+        <v>0.00155377</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>0.00155377</v>
+        <v>0.001511</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>0.001511</v>
+        <v>0.00131144</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>0.00131144</v>
+        <v>0.00142548</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>0.00142548</v>
-      </c>
-      <c r="AF17" s="13" t="n">
         <v>7.61341</v>
       </c>
-      <c r="AH17" s="13" t="n">
+      <c r="AG17" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH17" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI17" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ17" s="13" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
@@ -2451,81 +2381,80 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>CV measured NHO/PAU</t>
-        </is>
-      </c>
-      <c r="L18" s="13" t="n"/>
+          <t>measured by NHO/PAU</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.00410537</v>
+      </c>
       <c r="N18" s="13" t="n">
-        <v>0.00410537</v>
+        <v>0.00342114</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0.00342114</v>
+        <v>0.00329285</v>
       </c>
       <c r="P18" s="13" t="n">
-        <v>0.00329285</v>
+        <v>0.00307903</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.00285095</v>
       </c>
       <c r="R18" s="13" t="n">
-        <v>0.00285095</v>
+        <v>0.00263713</v>
       </c>
       <c r="S18" s="13" t="n">
-        <v>0.00263713</v>
+        <v>0.0023948</v>
       </c>
       <c r="T18" s="13" t="n">
-        <v>0.0023948</v>
+        <v>0.0021097</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>0.0021097</v>
+        <v>0.00198141</v>
       </c>
       <c r="V18" s="13" t="n">
         <v>0.00198141</v>
       </c>
       <c r="W18" s="13" t="n">
-        <v>0.00198141</v>
+        <v>0.00193865</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>0.00193865</v>
+        <v>0.00189588</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>0.00189588</v>
+        <v>0.00200992</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>0.00200992</v>
+        <v>0.00149675</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>0.00149675</v>
+        <v>0.00166781</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>0.00166781</v>
+        <v>0.001511</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>0.001511</v>
+        <v>0.00142548</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>0.00142548</v>
+        <v>0.00153951</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>0.00153951</v>
-      </c>
-      <c r="AF18" s="13" t="n">
         <v>8.53468</v>
       </c>
-      <c r="AH18" s="13" t="n">
+      <c r="AG18" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH18" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI18" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ18" s="13" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
@@ -2560,81 +2489,80 @@
       <c r="I19" s="13" t="n"/>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>ugly CV measured</t>
-        </is>
-      </c>
-      <c r="L19" s="13" t="n"/>
+          <t>poor-quality voltammogram</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0751511</v>
+      </c>
       <c r="N19" s="13" t="n">
-        <v>0.0751511</v>
+        <v>0.0491504</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0.0491504</v>
+        <v>0.0321445</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>0.0321445</v>
+        <v>0.0258866</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.0258866</v>
+        <v>0.0168776</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>0.0168776</v>
+        <v>0.01119</v>
       </c>
       <c r="S19" s="13" t="n">
-        <v>0.01119</v>
+        <v>0.00444749</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>0.00444749</v>
+        <v>0.00245182</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>0.00245182</v>
+        <v>0.00198141</v>
       </c>
       <c r="V19" s="13" t="n">
         <v>0.00198141</v>
       </c>
       <c r="W19" s="13" t="n">
-        <v>0.00198141</v>
+        <v>0.00182461</v>
       </c>
       <c r="X19" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00189588</v>
       </c>
       <c r="Y19" s="13" t="n">
-        <v>0.00189588</v>
+        <v>0.00178185</v>
       </c>
       <c r="Z19" s="13" t="n">
+        <v>0.00161079</v>
+      </c>
+      <c r="AA19" s="13" t="n">
         <v>0.00178185</v>
       </c>
-      <c r="AA19" s="13" t="n">
-        <v>0.00161079</v>
-      </c>
       <c r="AB19" s="13" t="n">
-        <v>0.00178185</v>
+        <v>0.00162504</v>
       </c>
       <c r="AC19" s="13" t="n">
-        <v>0.00162504</v>
+        <v>0.00165355</v>
       </c>
       <c r="AD19" s="13" t="n">
-        <v>0.00165355</v>
+        <v>0.00199567</v>
       </c>
       <c r="AE19" s="13" t="n">
-        <v>0.00199567</v>
-      </c>
-      <c r="AF19" s="13" t="n">
         <v>5.9514</v>
       </c>
-      <c r="AH19" s="13" t="n">
+      <c r="AG19" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH19" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI19" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ19" s="13" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
@@ -2669,81 +2597,76 @@
       <c r="I20" s="13" t="n"/>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L20" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n"/>
+      <c r="M20" s="13" t="n">
+        <v>0.00205269</v>
+      </c>
       <c r="N20" s="13" t="n">
-        <v>0.00205269</v>
+        <v>0.00182461</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00158228</v>
       </c>
       <c r="P20" s="13" t="n">
-        <v>0.00158228</v>
+        <v>0.00159653</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.00136846</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>0.00136846</v>
+        <v>0.00115464</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>0.00115464</v>
+        <v>0.00125442</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.00108336</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>0.00108336</v>
+        <v>0.000955069</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>0.000955069</v>
+        <v>0.00106911</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>0.00106911</v>
+        <v>0.00102634</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>0.00102634</v>
+        <v>0.00109762</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>0.00109762</v>
+        <v>0.00121165</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>0.00121165</v>
+        <v>0.0010406</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>0.0010406</v>
+        <v>0.0009835790000000001</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>0.0009835790000000001</v>
+        <v>0.000940814</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>0.000940814</v>
+        <v>0.000855286</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>0.000855286</v>
+        <v>0.000969324</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>0.000969324</v>
-      </c>
-      <c r="AF20" s="13" t="n">
         <v>4.34783</v>
       </c>
-      <c r="AH20" s="13" t="n">
+      <c r="AG20" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH20" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI20" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ20" s="13" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
@@ -2787,76 +2710,75 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>ask RET</t>
-        </is>
-      </c>
-      <c r="L21" s="13" t="n"/>
+          <t>no source recorded (lab record: 'ask RET')</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.00136846</v>
+      </c>
       <c r="N21" s="13" t="n">
         <v>0.00136846</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0.00136846</v>
+        <v>0.00112613</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>0.00112613</v>
+        <v>0.00114038</v>
       </c>
       <c r="Q21" s="13" t="n">
         <v>0.00114038</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.0010406</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>0.0010406</v>
+        <v>0.000912305</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.000855286</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>0.000855286</v>
+        <v>0.000955069</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>0.000955069</v>
+        <v>0.000841031</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>0.000841031</v>
+        <v>0.000798267</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.00086954</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>0.00086954</v>
+        <v>0.000755502</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>0.000755502</v>
+        <v>0.000698483</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>0.000698483</v>
+        <v>0.000641464</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>0.000641464</v>
+        <v>0.000712738</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>0.000712738</v>
+        <v>0.000741248</v>
       </c>
       <c r="AD21" s="13" t="n">
         <v>0.000741248</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>0.000741248</v>
-      </c>
-      <c r="AF21" s="13" t="n">
         <v>7.53066</v>
       </c>
-      <c r="AH21" s="13" t="n">
+      <c r="AG21" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH21" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI21" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ21" s="13" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
@@ -2891,81 +2813,76 @@
       <c r="I22" s="13" t="n"/>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>https://pubs.acs.org/doi/10.1021/ja00417a017</t>
-        </is>
-      </c>
-      <c r="L22" s="13" t="n"/>
+          <t>https://doi.org/10.1021/ja00417a017</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n"/>
+      <c r="M22" s="13" t="n">
+        <v>0.0023948</v>
+      </c>
       <c r="N22" s="13" t="n">
         <v>0.0023948</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>0.0023948</v>
+        <v>0.00215247</v>
       </c>
       <c r="P22" s="13" t="n">
-        <v>0.00215247</v>
+        <v>0.00216672</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.00205269</v>
       </c>
       <c r="R22" s="13" t="n">
-        <v>0.00205269</v>
+        <v>0.0019529</v>
       </c>
       <c r="S22" s="13" t="n">
-        <v>0.0019529</v>
+        <v>0.00182461</v>
       </c>
       <c r="T22" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00188163</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>0.00188163</v>
+        <v>0.00175334</v>
       </c>
       <c r="V22" s="13" t="n">
         <v>0.00175334</v>
       </c>
       <c r="W22" s="13" t="n">
-        <v>0.00175334</v>
+        <v>0.00171057</v>
       </c>
       <c r="X22" s="13" t="n">
-        <v>0.00171057</v>
+        <v>0.00178185</v>
       </c>
       <c r="Y22" s="13" t="n">
         <v>0.00178185</v>
       </c>
       <c r="Z22" s="13" t="n">
-        <v>0.00178185</v>
+        <v>0.00149675</v>
       </c>
       <c r="AA22" s="13" t="n">
-        <v>0.00149675</v>
+        <v>0.00166781</v>
       </c>
       <c r="AB22" s="13" t="n">
-        <v>0.00166781</v>
+        <v>0.00162504</v>
       </c>
       <c r="AC22" s="13" t="n">
-        <v>0.00162504</v>
+        <v>0.00165355</v>
       </c>
       <c r="AD22" s="13" t="n">
         <v>0.00165355</v>
       </c>
       <c r="AE22" s="13" t="n">
-        <v>0.00165355</v>
-      </c>
-      <c r="AF22" s="13" t="n">
         <v>7.26163</v>
       </c>
-      <c r="AH22" s="13" t="n">
+      <c r="AG22" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH22" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI22" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ22" s="13" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
@@ -3000,81 +2917,76 @@
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n"/>
+      <c r="M23" s="13" t="n">
+        <v>0.00125442</v>
+      </c>
       <c r="N23" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.00114038</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.00089805</v>
       </c>
       <c r="P23" s="13" t="n">
-        <v>0.00089805</v>
+        <v>0.000912305</v>
       </c>
       <c r="Q23" s="13" t="n">
         <v>0.000912305</v>
       </c>
       <c r="R23" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.000698483</v>
       </c>
       <c r="S23" s="13" t="n">
-        <v>0.000698483</v>
+        <v>0.000456152</v>
       </c>
       <c r="T23" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000513171</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>0.000513171</v>
+        <v>0.000384879</v>
       </c>
       <c r="V23" s="13" t="n">
         <v>0.000384879</v>
       </c>
       <c r="W23" s="13" t="n">
-        <v>0.000384879</v>
+        <v>0.00057019</v>
       </c>
       <c r="X23" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.00029935</v>
       </c>
       <c r="Y23" s="13" t="n">
+        <v>0.000413388</v>
+      </c>
+      <c r="Z23" s="13" t="n">
+        <v>0.000356369</v>
+      </c>
+      <c r="AA23" s="13" t="n">
         <v>0.00029935</v>
       </c>
-      <c r="Z23" s="13" t="n">
-        <v>0.000413388</v>
-      </c>
-      <c r="AA23" s="13" t="n">
-        <v>0.000356369</v>
-      </c>
       <c r="AB23" s="13" t="n">
-        <v>0.00029935</v>
+        <v>0.000256586</v>
       </c>
       <c r="AC23" s="13" t="n">
-        <v>0.000256586</v>
+        <v>0.000285095</v>
       </c>
       <c r="AD23" s="13" t="n">
-        <v>0.000285095</v>
+        <v>0.000399133</v>
       </c>
       <c r="AE23" s="13" t="n">
-        <v>0.000399133</v>
-      </c>
-      <c r="AF23" s="13" t="n">
         <v>7.80625</v>
       </c>
-      <c r="AH23" s="13" t="n">
+      <c r="AG23" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH23" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI23" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ23" s="13" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
@@ -3109,81 +3021,76 @@
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n"/>
+      <c r="M24" s="13" t="n">
+        <v>0.00307903</v>
+      </c>
       <c r="N24" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.0023948</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>0.0023948</v>
+        <v>0.00203843</v>
       </c>
       <c r="P24" s="13" t="n">
-        <v>0.00203843</v>
+        <v>0.00182461</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.00159653</v>
       </c>
       <c r="R24" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.00149675</v>
       </c>
       <c r="S24" s="13" t="n">
-        <v>0.00149675</v>
+        <v>0.00125442</v>
       </c>
       <c r="T24" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.00108336</v>
       </c>
       <c r="U24" s="13" t="n">
-        <v>0.00108336</v>
+        <v>0.000955069</v>
       </c>
       <c r="V24" s="13" t="n">
         <v>0.000955069</v>
       </c>
       <c r="W24" s="13" t="n">
-        <v>0.000955069</v>
+        <v>0.000912305</v>
       </c>
       <c r="X24" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.00086954</v>
       </c>
       <c r="Y24" s="13" t="n">
         <v>0.00086954</v>
       </c>
       <c r="Z24" s="13" t="n">
-        <v>0.00086954</v>
+        <v>0.000698483</v>
       </c>
       <c r="AA24" s="13" t="n">
-        <v>0.000698483</v>
+        <v>0.000641464</v>
       </c>
       <c r="AB24" s="13" t="n">
-        <v>0.000641464</v>
+        <v>0.0005987</v>
       </c>
       <c r="AC24" s="13" t="n">
-        <v>0.0005987</v>
+        <v>0.000627209</v>
       </c>
       <c r="AD24" s="13" t="n">
-        <v>0.000627209</v>
+        <v>0.000513171</v>
       </c>
       <c r="AE24" s="13" t="n">
-        <v>0.000513171</v>
-      </c>
-      <c r="AF24" s="13" t="n">
         <v>7.26163</v>
       </c>
-      <c r="AH24" s="13" t="n">
+      <c r="AG24" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH24" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI24" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ24" s="13" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
@@ -3218,81 +3125,76 @@
       <c r="I25" s="13" t="n"/>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L25" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n"/>
+      <c r="M25" s="13" t="n">
+        <v>0.00193865</v>
+      </c>
       <c r="N25" s="13" t="n">
-        <v>0.00193865</v>
+        <v>0.00159653</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.00158228</v>
       </c>
       <c r="P25" s="13" t="n">
-        <v>0.00158228</v>
+        <v>0.00136846</v>
       </c>
       <c r="Q25" s="13" t="n">
         <v>0.00136846</v>
       </c>
       <c r="R25" s="13" t="n">
-        <v>0.00136846</v>
+        <v>0.00126867</v>
       </c>
       <c r="S25" s="13" t="n">
-        <v>0.00126867</v>
+        <v>0.00102634</v>
       </c>
       <c r="T25" s="13" t="n">
-        <v>0.00102634</v>
+        <v>0.000969324</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>0.000969324</v>
+        <v>0.000955069</v>
       </c>
       <c r="V25" s="13" t="n">
         <v>0.000955069</v>
       </c>
       <c r="W25" s="13" t="n">
-        <v>0.000955069</v>
+        <v>0.000798267</v>
       </c>
       <c r="X25" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.00086954</v>
       </c>
       <c r="Y25" s="13" t="n">
-        <v>0.00086954</v>
+        <v>0.0009835790000000001</v>
       </c>
       <c r="Z25" s="13" t="n">
-        <v>0.0009835790000000001</v>
+        <v>0.000698483</v>
       </c>
       <c r="AA25" s="13" t="n">
-        <v>0.000698483</v>
+        <v>0.000755502</v>
       </c>
       <c r="AB25" s="13" t="n">
-        <v>0.000755502</v>
+        <v>0.0005987</v>
       </c>
       <c r="AC25" s="13" t="n">
-        <v>0.0005987</v>
+        <v>0.000627209</v>
       </c>
       <c r="AD25" s="13" t="n">
         <v>0.000627209</v>
       </c>
       <c r="AE25" s="13" t="n">
-        <v>0.000627209</v>
-      </c>
-      <c r="AF25" s="13" t="n">
         <v>5.58851</v>
       </c>
-      <c r="AH25" s="13" t="n">
+      <c r="AG25" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH25" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI25" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ25" s="13" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
@@ -3327,81 +3229,76 @@
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L26" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n"/>
+      <c r="M26" s="13" t="n">
+        <v>0.00342114</v>
+      </c>
       <c r="N26" s="13" t="n">
-        <v>0.00342114</v>
+        <v>0.00307903</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.00295074</v>
       </c>
       <c r="P26" s="13" t="n">
-        <v>0.00295074</v>
+        <v>0.00285095</v>
       </c>
       <c r="Q26" s="13" t="n">
         <v>0.00285095</v>
       </c>
       <c r="R26" s="13" t="n">
-        <v>0.00285095</v>
+        <v>0.00263713</v>
       </c>
       <c r="S26" s="13" t="n">
-        <v>0.00263713</v>
+        <v>0.00250884</v>
       </c>
       <c r="T26" s="13" t="n">
-        <v>0.00250884</v>
+        <v>0.00222374</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>0.00222374</v>
+        <v>0.00220949</v>
       </c>
       <c r="V26" s="13" t="n">
         <v>0.00220949</v>
       </c>
       <c r="W26" s="13" t="n">
-        <v>0.00220949</v>
+        <v>0.00228076</v>
       </c>
       <c r="X26" s="13" t="n">
-        <v>0.00228076</v>
+        <v>0.00212396</v>
       </c>
       <c r="Y26" s="13" t="n">
-        <v>0.00212396</v>
+        <v>0.002238</v>
       </c>
       <c r="Z26" s="13" t="n">
-        <v>0.002238</v>
+        <v>0.0019529</v>
       </c>
       <c r="AA26" s="13" t="n">
-        <v>0.0019529</v>
+        <v>0.00200992</v>
       </c>
       <c r="AB26" s="13" t="n">
-        <v>0.00200992</v>
+        <v>0.00185312</v>
       </c>
       <c r="AC26" s="13" t="n">
-        <v>0.00185312</v>
+        <v>0.00188163</v>
       </c>
       <c r="AD26" s="13" t="n">
         <v>0.00188163</v>
       </c>
       <c r="AE26" s="13" t="n">
-        <v>0.00188163</v>
-      </c>
-      <c r="AF26" s="13" t="n">
         <v>11.2471</v>
       </c>
-      <c r="AH26" s="13" t="n">
+      <c r="AG26" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH26" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI26" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ26" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
@@ -3436,7 +3333,7 @@
       <c r="I27" s="13" t="n"/>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -3444,73 +3341,72 @@
           <t>measured by TJS</t>
         </is>
       </c>
-      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="n">
+        <v>0.00182461</v>
+      </c>
       <c r="N27" s="13" t="n">
-        <v>0.00182461</v>
+        <v>0.0014825</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>0.0014825</v>
+        <v>0.00124016</v>
       </c>
       <c r="P27" s="13" t="n">
-        <v>0.00124016</v>
+        <v>0.00125442</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.00102634</v>
       </c>
       <c r="R27" s="13" t="n">
-        <v>0.00102634</v>
+        <v>0.0010406</v>
       </c>
       <c r="S27" s="13" t="n">
-        <v>0.0010406</v>
+        <v>0.000912305</v>
       </c>
       <c r="T27" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.00108336</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>0.00108336</v>
+        <v>0.000955069</v>
       </c>
       <c r="V27" s="13" t="n">
         <v>0.000955069</v>
       </c>
       <c r="W27" s="13" t="n">
-        <v>0.000955069</v>
+        <v>0.00102634</v>
       </c>
       <c r="X27" s="13" t="n">
-        <v>0.00102634</v>
+        <v>0.0009835790000000001</v>
       </c>
       <c r="Y27" s="13" t="n">
         <v>0.0009835790000000001</v>
       </c>
       <c r="Z27" s="13" t="n">
-        <v>0.0009835790000000001</v>
+        <v>0.000926559</v>
       </c>
       <c r="AA27" s="13" t="n">
-        <v>0.000926559</v>
+        <v>0.00109762</v>
       </c>
       <c r="AB27" s="13" t="n">
-        <v>0.00109762</v>
+        <v>0.000940814</v>
       </c>
       <c r="AC27" s="13" t="n">
-        <v>0.000940814</v>
+        <v>0.00108336</v>
       </c>
       <c r="AD27" s="13" t="n">
         <v>0.00108336</v>
       </c>
       <c r="AE27" s="13" t="n">
-        <v>0.00108336</v>
-      </c>
-      <c r="AF27" s="13" t="n">
         <v>6.54654</v>
       </c>
-      <c r="AH27" s="13" t="n">
+      <c r="AG27" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH27" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI27" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ27" s="13" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
@@ -3549,7 +3445,7 @@
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -3557,73 +3453,72 @@
           <t>measured by TJS</t>
         </is>
       </c>
-      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n">
+        <v>0.00114038</v>
+      </c>
       <c r="N28" s="13" t="n">
         <v>0.00114038</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.00101209</v>
       </c>
       <c r="P28" s="13" t="n">
-        <v>0.00101209</v>
+        <v>0.000912305</v>
       </c>
       <c r="Q28" s="13" t="n">
         <v>0.000912305</v>
       </c>
       <c r="R28" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.000698483</v>
       </c>
       <c r="S28" s="13" t="n">
-        <v>0.000698483</v>
+        <v>0.000798267</v>
       </c>
       <c r="T28" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.000855286</v>
       </c>
       <c r="U28" s="13" t="n">
-        <v>0.000855286</v>
+        <v>0.000726993</v>
       </c>
       <c r="V28" s="13" t="n">
         <v>0.000726993</v>
       </c>
       <c r="W28" s="13" t="n">
-        <v>0.000726993</v>
+        <v>0.000798267</v>
       </c>
       <c r="X28" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.0009835790000000001</v>
       </c>
       <c r="Y28" s="13" t="n">
-        <v>0.0009835790000000001</v>
+        <v>0.000755502</v>
       </c>
       <c r="Z28" s="13" t="n">
-        <v>0.000755502</v>
+        <v>0.000584445</v>
       </c>
       <c r="AA28" s="13" t="n">
-        <v>0.000584445</v>
+        <v>0.00086954</v>
       </c>
       <c r="AB28" s="13" t="n">
-        <v>0.00086954</v>
+        <v>0.0005987</v>
       </c>
       <c r="AC28" s="13" t="n">
-        <v>0.0005987</v>
+        <v>0.000627209</v>
       </c>
       <c r="AD28" s="13" t="n">
-        <v>0.000627209</v>
+        <v>0.000741248</v>
       </c>
       <c r="AE28" s="13" t="n">
-        <v>0.000741248</v>
-      </c>
-      <c r="AF28" s="13" t="n">
         <v>6.83967</v>
       </c>
-      <c r="AH28" s="13" t="n">
+      <c r="AG28" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH28" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI28" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ28" s="13" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
@@ -3658,81 +3553,76 @@
       <c r="I29" s="13" t="n"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n"/>
+      <c r="M29" s="13" t="n">
+        <v>0.00296499</v>
+      </c>
       <c r="N29" s="13" t="n">
-        <v>0.00296499</v>
+        <v>0.00285095</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.00285095</v>
+        <v>0.00272266</v>
       </c>
       <c r="P29" s="13" t="n">
-        <v>0.00272266</v>
+        <v>0.00262288</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.00262288</v>
+        <v>0.0023948</v>
       </c>
       <c r="R29" s="13" t="n">
-        <v>0.0023948</v>
+        <v>0.00229502</v>
       </c>
       <c r="S29" s="13" t="n">
-        <v>0.00229502</v>
+        <v>0.00193865</v>
       </c>
       <c r="T29" s="13" t="n">
-        <v>0.00193865</v>
+        <v>0.00188163</v>
       </c>
       <c r="U29" s="13" t="n">
-        <v>0.00188163</v>
+        <v>0.00175334</v>
       </c>
       <c r="V29" s="13" t="n">
         <v>0.00175334</v>
       </c>
       <c r="W29" s="13" t="n">
-        <v>0.00175334</v>
+        <v>0.00171057</v>
       </c>
       <c r="X29" s="13" t="n">
-        <v>0.00171057</v>
+        <v>0.00178185</v>
       </c>
       <c r="Y29" s="13" t="n">
         <v>0.00178185</v>
       </c>
       <c r="Z29" s="13" t="n">
-        <v>0.00178185</v>
+        <v>0.00161079</v>
       </c>
       <c r="AA29" s="13" t="n">
-        <v>0.00161079</v>
+        <v>0.00155377</v>
       </c>
       <c r="AB29" s="13" t="n">
-        <v>0.00155377</v>
+        <v>0.00162504</v>
       </c>
       <c r="AC29" s="13" t="n">
-        <v>0.00162504</v>
+        <v>0.00153951</v>
       </c>
       <c r="AD29" s="13" t="n">
-        <v>0.00153951</v>
+        <v>0.00165355</v>
       </c>
       <c r="AE29" s="13" t="n">
-        <v>0.00165355</v>
-      </c>
-      <c r="AF29" s="13" t="n">
         <v>5.0358</v>
       </c>
-      <c r="AH29" s="13" t="n">
+      <c r="AG29" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH29" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI29" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ29" s="13" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
@@ -3771,81 +3661,76 @@
       <c r="I30" s="13" t="n"/>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L30" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n"/>
+      <c r="M30" s="13" t="n">
+        <v>0.104003</v>
+      </c>
       <c r="N30" s="13" t="n">
-        <v>0.104003</v>
+        <v>0.0459573</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>0.0459573</v>
+        <v>0.00602976</v>
       </c>
       <c r="P30" s="13" t="n">
-        <v>0.00602976</v>
+        <v>0.00228076</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.00228076</v>
+        <v>0.00114038</v>
       </c>
       <c r="R30" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.000812521</v>
       </c>
       <c r="S30" s="13" t="n">
-        <v>0.000812521</v>
+        <v>0.00057019</v>
       </c>
       <c r="T30" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.000513171</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>0.000513171</v>
+        <v>0.000498917</v>
       </c>
       <c r="V30" s="13" t="n">
         <v>0.000498917</v>
       </c>
       <c r="W30" s="13" t="n">
-        <v>0.000498917</v>
+        <v>0.000342114</v>
       </c>
       <c r="X30" s="13" t="n">
-        <v>0.000342114</v>
+        <v>0.000413388</v>
       </c>
       <c r="Y30" s="13" t="n">
-        <v>0.000413388</v>
+        <v>0.000527426</v>
       </c>
       <c r="Z30" s="13" t="n">
-        <v>0.000527426</v>
+        <v>0.000242331</v>
       </c>
       <c r="AA30" s="13" t="n">
-        <v>0.000242331</v>
+        <v>0.00029935</v>
       </c>
       <c r="AB30" s="13" t="n">
-        <v>0.00029935</v>
+        <v>0.000256586</v>
       </c>
       <c r="AC30" s="13" t="n">
-        <v>0.000256586</v>
+        <v>0.000285095</v>
       </c>
       <c r="AD30" s="13" t="n">
         <v>0.000285095</v>
       </c>
       <c r="AE30" s="13" t="n">
-        <v>0.000285095</v>
-      </c>
-      <c r="AF30" s="13" t="n">
         <v>5.41266</v>
       </c>
-      <c r="AH30" s="13" t="n">
+      <c r="AG30" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH30" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI30" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ30" s="13" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
@@ -3884,81 +3769,76 @@
       <c r="I31" s="13" t="n"/>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1021/jacs.4c18080</t>
         </is>
       </c>
       <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>Cyclic Bifunctional Reagents Enabling a Strain-Release-Driven Formal [3 + 2] Cycloaddition of 2H-Azirines by Cascade Energy Transfer | Journal of the American Chemical Society</t>
-        </is>
+      <c r="M31" s="13" t="n">
+        <v>0.000456152</v>
       </c>
       <c r="N31" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000342114</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0.000342114</v>
+        <v>0.000213821</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>0.000213821</v>
+        <v>0.000228076</v>
       </c>
       <c r="Q31" s="13" t="n">
         <v>0.000228076</v>
       </c>
       <c r="R31" s="13" t="n">
+        <v>0.000128293</v>
+      </c>
+      <c r="S31" s="13" t="n">
         <v>0.000228076</v>
       </c>
-      <c r="S31" s="13" t="n">
-        <v>0.000128293</v>
-      </c>
       <c r="T31" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.000171057</v>
       </c>
       <c r="U31" s="13" t="n">
-        <v>0.000171057</v>
+        <v>0.000156802</v>
       </c>
       <c r="V31" s="13" t="n">
         <v>0.000156802</v>
       </c>
       <c r="W31" s="13" t="n">
-        <v>0.000156802</v>
+        <v>0.000114038</v>
       </c>
       <c r="X31" s="13" t="n">
-        <v>0.000114038</v>
+        <v>0.000185312</v>
       </c>
       <c r="Y31" s="13" t="n">
         <v>0.000185312</v>
       </c>
       <c r="Z31" s="13" t="n">
+        <v>0.000128293</v>
+      </c>
+      <c r="AA31" s="13" t="n">
         <v>0.000185312</v>
       </c>
-      <c r="AA31" s="13" t="n">
-        <v>0.000128293</v>
-      </c>
       <c r="AB31" s="13" t="n">
-        <v>0.000185312</v>
+        <v>0.000142548</v>
       </c>
       <c r="AC31" s="13" t="n">
-        <v>0.000142548</v>
+        <v>0.000171057</v>
       </c>
       <c r="AD31" s="13" t="n">
         <v>0.000171057</v>
       </c>
       <c r="AE31" s="13" t="n">
-        <v>0.000171057</v>
-      </c>
-      <c r="AF31" s="13" t="n">
         <v>4.7619</v>
       </c>
-      <c r="AH31" s="13" t="n">
+      <c r="AG31" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH31" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI31" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ31" s="13" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
@@ -3993,81 +3873,76 @@
       <c r="I32" s="13" t="n"/>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1039/d2sc05229f</t>
         </is>
       </c>
       <c r="K32" s="13" t="n"/>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>Sensitizer-controlled photochemical reactivity via upconversion of red light - Chemical Science (RSC Publishing)</t>
-        </is>
+      <c r="M32" s="13" t="n">
+        <v>0.00114038</v>
       </c>
       <c r="N32" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.000798267</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.000669974</v>
       </c>
       <c r="P32" s="13" t="n">
-        <v>0.000669974</v>
+        <v>0.00057019</v>
       </c>
       <c r="Q32" s="13" t="n">
         <v>0.00057019</v>
       </c>
       <c r="R32" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.000470407</v>
       </c>
       <c r="S32" s="13" t="n">
-        <v>0.000470407</v>
+        <v>0.000456152</v>
       </c>
       <c r="T32" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000399133</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>0.000399133</v>
+        <v>0.000384879</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>0.000384879</v>
+        <v>0.00027084</v>
       </c>
       <c r="W32" s="13" t="n">
-        <v>0.00027084</v>
+        <v>0.000228076</v>
       </c>
       <c r="X32" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.00029935</v>
       </c>
       <c r="Y32" s="13" t="n">
-        <v>0.00029935</v>
+        <v>0.000413388</v>
       </c>
       <c r="Z32" s="13" t="n">
-        <v>0.000413388</v>
+        <v>0.000128293</v>
       </c>
       <c r="AA32" s="13" t="n">
-        <v>0.000128293</v>
+        <v>0.000185312</v>
       </c>
       <c r="AB32" s="13" t="n">
-        <v>0.000185312</v>
+        <v>0.000142548</v>
       </c>
       <c r="AC32" s="13" t="n">
-        <v>0.000142548</v>
+        <v>0.000171057</v>
       </c>
       <c r="AD32" s="13" t="n">
         <v>0.000171057</v>
       </c>
       <c r="AE32" s="13" t="n">
-        <v>0.000171057</v>
-      </c>
-      <c r="AF32" s="13" t="n">
         <v>6.54654</v>
       </c>
-      <c r="AH32" s="13" t="n">
+      <c r="AG32" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH32" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI32" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ32" s="13" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
@@ -4110,81 +3985,80 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>CV measured by NHO</t>
-        </is>
-      </c>
-      <c r="L33" s="13" t="n"/>
+          <t>measured by NHO</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.00159653</v>
+      </c>
       <c r="N33" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.00125442</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.00124016</v>
       </c>
       <c r="P33" s="13" t="n">
-        <v>0.00124016</v>
+        <v>0.00114038</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.00102634</v>
       </c>
       <c r="R33" s="13" t="n">
-        <v>0.00102634</v>
+        <v>0.000812521</v>
       </c>
       <c r="S33" s="13" t="n">
-        <v>0.000812521</v>
+        <v>0.000798267</v>
       </c>
       <c r="T33" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.000627209</v>
       </c>
       <c r="U33" s="13" t="n">
-        <v>0.000627209</v>
+        <v>0.000612955</v>
       </c>
       <c r="V33" s="13" t="n">
-        <v>0.000612955</v>
+        <v>0.000498917</v>
       </c>
       <c r="W33" s="13" t="n">
-        <v>0.000498917</v>
+        <v>0.00057019</v>
       </c>
       <c r="X33" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.000641464</v>
       </c>
       <c r="Y33" s="13" t="n">
-        <v>0.000641464</v>
+        <v>0.000527426</v>
       </c>
       <c r="Z33" s="13" t="n">
-        <v>0.000527426</v>
+        <v>0.000356369</v>
       </c>
       <c r="AA33" s="13" t="n">
-        <v>0.000356369</v>
+        <v>0.000413388</v>
       </c>
       <c r="AB33" s="13" t="n">
-        <v>0.000413388</v>
+        <v>0.000370624</v>
       </c>
       <c r="AC33" s="13" t="n">
-        <v>0.000370624</v>
+        <v>0.000399133</v>
       </c>
       <c r="AD33" s="13" t="n">
-        <v>0.000399133</v>
+        <v>0.000285095</v>
       </c>
       <c r="AE33" s="13" t="n">
-        <v>0.000285095</v>
-      </c>
-      <c r="AF33" s="13" t="n">
         <v>5.32939</v>
       </c>
-      <c r="AH33" s="13" t="n">
+      <c r="AG33" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH33" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI33" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ33" s="13" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
@@ -4228,76 +4102,75 @@
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>estimated from Leandro Thioamides</t>
-        </is>
-      </c>
-      <c r="L34" s="13" t="n"/>
+          <t>estimated from Leandro's thioamides; no reference recorded</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.285779</v>
+      </c>
       <c r="N34" s="13" t="n">
-        <v>0.285779</v>
+        <v>0.207891</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0.207891</v>
+        <v>0.123717</v>
       </c>
       <c r="P34" s="13" t="n">
-        <v>0.123717</v>
+        <v>0.0888357</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.0888357</v>
+        <v>0.0410537</v>
       </c>
       <c r="R34" s="13" t="n">
-        <v>0.0410537</v>
+        <v>0.0167779</v>
       </c>
       <c r="S34" s="13" t="n">
-        <v>0.0167779</v>
+        <v>0.00216672</v>
       </c>
       <c r="T34" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.0011974</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>0.0011974</v>
+        <v>0.00106911</v>
       </c>
       <c r="V34" s="13" t="n">
         <v>0.00106911</v>
       </c>
       <c r="W34" s="13" t="n">
-        <v>0.00106911</v>
+        <v>0.000912305</v>
       </c>
       <c r="X34" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.0009835790000000001</v>
       </c>
       <c r="Y34" s="13" t="n">
         <v>0.0009835790000000001</v>
       </c>
       <c r="Z34" s="13" t="n">
-        <v>0.0009835790000000001</v>
+        <v>0.000812521</v>
       </c>
       <c r="AA34" s="13" t="n">
-        <v>0.000812521</v>
+        <v>0.00086954</v>
       </c>
       <c r="AB34" s="13" t="n">
-        <v>0.00086954</v>
+        <v>0.000712738</v>
       </c>
       <c r="AC34" s="13" t="n">
-        <v>0.000712738</v>
+        <v>0.000741248</v>
       </c>
       <c r="AD34" s="13" t="n">
         <v>0.000741248</v>
       </c>
       <c r="AE34" s="13" t="n">
-        <v>0.000741248</v>
-      </c>
-      <c r="AF34" s="13" t="n">
         <v>7.53066</v>
       </c>
-      <c r="AH34" s="13" t="n">
+      <c r="AG34" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH34" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI34" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ34" s="13" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
@@ -4341,76 +4214,75 @@
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>estimated from Leandro Thioamides</t>
-        </is>
-      </c>
-      <c r="L35" s="13" t="n"/>
+          <t>estimated from Leandro's thioamides; no reference recorded</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0401414</v>
+      </c>
       <c r="N35" s="13" t="n">
-        <v>0.0401414</v>
+        <v>0.0191584</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>0.0191584</v>
+        <v>0.00796841</v>
       </c>
       <c r="P35" s="13" t="n">
-        <v>0.00796841</v>
+        <v>0.00490364</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.00490364</v>
+        <v>0.00205269</v>
       </c>
       <c r="R35" s="13" t="n">
-        <v>0.00205269</v>
+        <v>0.00115464</v>
       </c>
       <c r="S35" s="13" t="n">
-        <v>0.00115464</v>
+        <v>0.000798267</v>
       </c>
       <c r="T35" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.000627209</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>0.000627209</v>
+        <v>0.000612955</v>
       </c>
       <c r="V35" s="13" t="n">
         <v>0.000612955</v>
       </c>
       <c r="W35" s="13" t="n">
-        <v>0.000612955</v>
+        <v>0.00057019</v>
       </c>
       <c r="X35" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.000641464</v>
       </c>
       <c r="Y35" s="13" t="n">
-        <v>0.000641464</v>
+        <v>0.000527426</v>
       </c>
       <c r="Z35" s="13" t="n">
+        <v>0.000584445</v>
+      </c>
+      <c r="AA35" s="13" t="n">
         <v>0.000527426</v>
       </c>
-      <c r="AA35" s="13" t="n">
-        <v>0.000584445</v>
-      </c>
       <c r="AB35" s="13" t="n">
-        <v>0.000527426</v>
+        <v>0.0005987</v>
       </c>
       <c r="AC35" s="13" t="n">
-        <v>0.0005987</v>
+        <v>0.000513171</v>
       </c>
       <c r="AD35" s="13" t="n">
         <v>0.000513171</v>
       </c>
       <c r="AE35" s="13" t="n">
-        <v>0.000513171</v>
-      </c>
-      <c r="AF35" s="13" t="n">
         <v>4.54545</v>
       </c>
-      <c r="AH35" s="13" t="n">
+      <c r="AG35" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH35" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI35" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ35" s="13" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
@@ -4445,81 +4317,76 @@
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L36" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n"/>
+      <c r="M36" s="13" t="n">
+        <v>0.00114038</v>
+      </c>
       <c r="N36" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.000798267</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.000669974</v>
       </c>
       <c r="P36" s="13" t="n">
-        <v>0.000669974</v>
+        <v>0.000684229</v>
       </c>
       <c r="Q36" s="13" t="n">
         <v>0.000684229</v>
       </c>
       <c r="R36" s="13" t="n">
-        <v>0.000684229</v>
+        <v>0.000584445</v>
       </c>
       <c r="S36" s="13" t="n">
-        <v>0.000584445</v>
+        <v>0.000456152</v>
       </c>
       <c r="T36" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000513171</v>
       </c>
       <c r="U36" s="13" t="n">
-        <v>0.000513171</v>
+        <v>0.000498917</v>
       </c>
       <c r="V36" s="13" t="n">
         <v>0.000498917</v>
       </c>
       <c r="W36" s="13" t="n">
-        <v>0.000498917</v>
+        <v>0.00057019</v>
       </c>
       <c r="X36" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.000527426</v>
       </c>
       <c r="Y36" s="13" t="n">
-        <v>0.000527426</v>
+        <v>0.000413388</v>
       </c>
       <c r="Z36" s="13" t="n">
+        <v>0.000356369</v>
+      </c>
+      <c r="AA36" s="13" t="n">
         <v>0.000413388</v>
       </c>
-      <c r="AA36" s="13" t="n">
-        <v>0.000356369</v>
-      </c>
       <c r="AB36" s="13" t="n">
-        <v>0.000413388</v>
+        <v>0.000484662</v>
       </c>
       <c r="AC36" s="13" t="n">
-        <v>0.000484662</v>
+        <v>0.000399133</v>
       </c>
       <c r="AD36" s="13" t="n">
         <v>0.000399133</v>
       </c>
       <c r="AE36" s="13" t="n">
-        <v>0.000399133</v>
-      </c>
-      <c r="AF36" s="13" t="n">
         <v>6.0297</v>
       </c>
-      <c r="AH36" s="13" t="n">
+      <c r="AG36" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH36" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI36" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ36" s="13" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
@@ -4554,81 +4421,76 @@
       <c r="I37" s="13" t="n"/>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1039/d2sc05229f</t>
         </is>
       </c>
       <c r="K37" s="13" t="n"/>
-      <c r="L37" s="13" t="inlineStr">
-        <is>
-          <t>Sensitizer-controlled photochemical reactivity via upconversion of red light - Chemical Science (RSC Publishing)</t>
-        </is>
+      <c r="M37" s="13" t="n">
+        <v>0.00102634</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>0.00102634</v>
+        <v>0.000684229</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>0.000684229</v>
+        <v>0.000555936</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>0.000555936</v>
+        <v>0.000456152</v>
       </c>
       <c r="Q37" s="13" t="n">
         <v>0.000456152</v>
       </c>
       <c r="R37" s="13" t="n">
+        <v>0.000470407</v>
+      </c>
+      <c r="S37" s="13" t="n">
         <v>0.000456152</v>
       </c>
-      <c r="S37" s="13" t="n">
-        <v>0.000470407</v>
-      </c>
       <c r="T37" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000399133</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>0.000399133</v>
+        <v>0.000384879</v>
       </c>
       <c r="V37" s="13" t="n">
         <v>0.000384879</v>
       </c>
       <c r="W37" s="13" t="n">
-        <v>0.000384879</v>
+        <v>0.000228076</v>
       </c>
       <c r="X37" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.00029935</v>
       </c>
       <c r="Y37" s="13" t="n">
-        <v>0.00029935</v>
+        <v>0.000185312</v>
       </c>
       <c r="Z37" s="13" t="n">
+        <v>0.000242331</v>
+      </c>
+      <c r="AA37" s="13" t="n">
         <v>0.000185312</v>
       </c>
-      <c r="AA37" s="13" t="n">
-        <v>0.000242331</v>
-      </c>
       <c r="AB37" s="13" t="n">
-        <v>0.000185312</v>
+        <v>0.000256586</v>
       </c>
       <c r="AC37" s="13" t="n">
-        <v>0.000256586</v>
+        <v>5.7019e-05</v>
       </c>
       <c r="AD37" s="13" t="n">
         <v>5.7019e-05</v>
       </c>
       <c r="AE37" s="13" t="n">
-        <v>5.7019e-05</v>
-      </c>
-      <c r="AF37" s="13" t="n">
         <v>6.2775</v>
       </c>
-      <c r="AH37" s="13" t="n">
+      <c r="AG37" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH37" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI37" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ37" s="13" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
@@ -4663,81 +4525,76 @@
       <c r="I38" s="13" t="n"/>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L38" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n"/>
+      <c r="M38" s="13" t="n">
+        <v>0.000912305</v>
+      </c>
       <c r="N38" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.000684229</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.000684229</v>
+        <v>0.000555936</v>
       </c>
       <c r="P38" s="13" t="n">
-        <v>0.000555936</v>
+        <v>0.00057019</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.000456152</v>
       </c>
       <c r="R38" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000470407</v>
       </c>
       <c r="S38" s="13" t="n">
-        <v>0.000470407</v>
+        <v>0.000228076</v>
       </c>
       <c r="T38" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.000285095</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>0.000285095</v>
+        <v>0.00027084</v>
       </c>
       <c r="V38" s="13" t="n">
         <v>0.00027084</v>
       </c>
       <c r="W38" s="13" t="n">
-        <v>0.00027084</v>
+        <v>0.000342114</v>
       </c>
       <c r="X38" s="13" t="n">
-        <v>0.000342114</v>
+        <v>0.000413388</v>
       </c>
       <c r="Y38" s="13" t="n">
-        <v>0.000413388</v>
+        <v>0.000185312</v>
       </c>
       <c r="Z38" s="13" t="n">
-        <v>0.000185312</v>
+        <v>0.000128293</v>
       </c>
       <c r="AA38" s="13" t="n">
-        <v>0.000128293</v>
+        <v>0.00029935</v>
       </c>
       <c r="AB38" s="13" t="n">
-        <v>0.00029935</v>
+        <v>0.000142548</v>
       </c>
       <c r="AC38" s="13" t="n">
-        <v>0.000142548</v>
+        <v>0.000171057</v>
       </c>
       <c r="AD38" s="13" t="n">
         <v>0.000171057</v>
       </c>
       <c r="AE38" s="13" t="n">
-        <v>0.000171057</v>
-      </c>
-      <c r="AF38" s="13" t="n">
         <v>4.49883</v>
       </c>
-      <c r="AH38" s="13" t="n">
+      <c r="AG38" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH38" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI38" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ38" s="13" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
@@ -4772,81 +4629,76 @@
       <c r="I39" s="13" t="n"/>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n"/>
+      <c r="M39" s="13" t="n">
+        <v>0.0172198</v>
+      </c>
       <c r="N39" s="13" t="n">
-        <v>0.0172198</v>
+        <v>0.0140267</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>0.0140267</v>
+        <v>0.0116176</v>
       </c>
       <c r="P39" s="13" t="n">
-        <v>0.0116176</v>
+        <v>0.0106055</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.0106055</v>
+        <v>0.00900901</v>
       </c>
       <c r="R39" s="13" t="n">
-        <v>0.00900901</v>
+        <v>0.00765481</v>
       </c>
       <c r="S39" s="13" t="n">
-        <v>0.00765481</v>
+        <v>0.00558787</v>
       </c>
       <c r="T39" s="13" t="n">
-        <v>0.00558787</v>
+        <v>0.00427643</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>0.00427643</v>
+        <v>0.00380602</v>
       </c>
       <c r="V39" s="13" t="n">
-        <v>0.00380602</v>
+        <v>0.00357795</v>
       </c>
       <c r="W39" s="13" t="n">
-        <v>0.00357795</v>
+        <v>0.0033071</v>
       </c>
       <c r="X39" s="13" t="n">
-        <v>0.0033071</v>
+        <v>0.0031503</v>
       </c>
       <c r="Y39" s="13" t="n">
-        <v>0.0031503</v>
+        <v>0.00292223</v>
       </c>
       <c r="Z39" s="13" t="n">
-        <v>0.00292223</v>
+        <v>0.0019529</v>
       </c>
       <c r="AA39" s="13" t="n">
-        <v>0.0019529</v>
+        <v>0.00189588</v>
       </c>
       <c r="AB39" s="13" t="n">
-        <v>0.00189588</v>
+        <v>0.00173908</v>
       </c>
       <c r="AC39" s="13" t="n">
-        <v>0.00173908</v>
+        <v>0.00165355</v>
       </c>
       <c r="AD39" s="13" t="n">
-        <v>0.00165355</v>
+        <v>0.00131144</v>
       </c>
       <c r="AE39" s="13" t="n">
-        <v>0.00131144</v>
-      </c>
-      <c r="AF39" s="13" t="n">
         <v>6.0297</v>
       </c>
-      <c r="AH39" s="13" t="n">
+      <c r="AG39" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH39" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI39" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ39" s="13" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
@@ -4885,81 +4737,80 @@
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="n"/>
-      <c r="L40" s="13" t="inlineStr">
-        <is>
-          <t>Oxidation from https://iopscience.iop.org/article/10.1149/1.2425951</t>
-        </is>
+          <t>https://doi.org/10.1149/1.2425951</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>oxidation only; the reduction bound is not attributed</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.000228076</v>
       </c>
       <c r="N40" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.000114038</v>
       </c>
       <c r="O40" s="13" t="n">
+        <v>9.97833e-05</v>
+      </c>
+      <c r="P40" s="13" t="n">
         <v>0.000114038</v>
-      </c>
-      <c r="P40" s="13" t="n">
-        <v>9.97833e-05</v>
       </c>
       <c r="Q40" s="13" t="n">
         <v>0.000114038</v>
       </c>
       <c r="R40" s="13" t="n">
+        <v>0.000128293</v>
+      </c>
+      <c r="S40" s="13" t="n">
         <v>0.000114038</v>
       </c>
-      <c r="S40" s="13" t="n">
-        <v>0.000128293</v>
-      </c>
       <c r="T40" s="13" t="n">
+        <v>0.000171057</v>
+      </c>
+      <c r="U40" s="13" t="n">
+        <v>0.000156802</v>
+      </c>
+      <c r="V40" s="13" t="n">
+        <v>4.27643e-05</v>
+      </c>
+      <c r="W40" s="13" t="n">
         <v>0.000114038</v>
       </c>
-      <c r="U40" s="13" t="n">
-        <v>0.000171057</v>
-      </c>
-      <c r="V40" s="13" t="n">
-        <v>0.000156802</v>
-      </c>
-      <c r="W40" s="13" t="n">
-        <v>4.27643e-05</v>
-      </c>
       <c r="X40" s="13" t="n">
-        <v>0.000114038</v>
+        <v>7.12738e-05</v>
       </c>
       <c r="Y40" s="13" t="n">
         <v>7.12738e-05</v>
       </c>
       <c r="Z40" s="13" t="n">
+        <v>-9.97833e-05</v>
+      </c>
+      <c r="AA40" s="13" t="n">
         <v>7.12738e-05</v>
       </c>
-      <c r="AA40" s="13" t="n">
-        <v>-9.97833e-05</v>
-      </c>
       <c r="AB40" s="13" t="n">
-        <v>7.12738e-05</v>
+        <v>-8.55286e-05</v>
       </c>
       <c r="AC40" s="13" t="n">
-        <v>-8.55286e-05</v>
+        <v>-5.7019e-05</v>
       </c>
       <c r="AD40" s="13" t="n">
         <v>-5.7019e-05</v>
       </c>
       <c r="AE40" s="13" t="n">
-        <v>-5.7019e-05</v>
-      </c>
-      <c r="AF40" s="13" t="n">
         <v>5.58726</v>
       </c>
-      <c r="AH40" s="13" t="n">
+      <c r="AG40" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH40" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI40" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ40" s="13" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
@@ -4994,81 +4845,76 @@
       <c r="I41" s="13" t="n"/>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L41" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n"/>
+      <c r="M41" s="13" t="n">
+        <v>0.00376326</v>
+      </c>
       <c r="N41" s="13" t="n">
-        <v>0.00376326</v>
+        <v>0.00307903</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.00238055</v>
       </c>
       <c r="P41" s="13" t="n">
-        <v>0.00238055</v>
+        <v>0.00193865</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.00193865</v>
+        <v>0.00125442</v>
       </c>
       <c r="R41" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.000698483</v>
       </c>
       <c r="S41" s="13" t="n">
-        <v>0.000698483</v>
+        <v>0.000228076</v>
       </c>
       <c r="T41" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.000285095</v>
       </c>
       <c r="U41" s="13" t="n">
-        <v>0.000285095</v>
+        <v>0.000156802</v>
       </c>
       <c r="V41" s="13" t="n">
         <v>0.000156802</v>
       </c>
       <c r="W41" s="13" t="n">
-        <v>0.000156802</v>
+        <v>1.38778e-18</v>
       </c>
       <c r="X41" s="13" t="n">
-        <v>1.38778e-18</v>
+        <v>7.12738e-05</v>
       </c>
       <c r="Y41" s="13" t="n">
         <v>7.12738e-05</v>
       </c>
       <c r="Z41" s="13" t="n">
+        <v>-9.97833e-05</v>
+      </c>
+      <c r="AA41" s="13" t="n">
         <v>7.12738e-05</v>
       </c>
-      <c r="AA41" s="13" t="n">
-        <v>-9.97833e-05</v>
-      </c>
       <c r="AB41" s="13" t="n">
-        <v>7.12738e-05</v>
+        <v>-8.55286e-05</v>
       </c>
       <c r="AC41" s="13" t="n">
-        <v>-8.55286e-05</v>
+        <v>-0.000171057</v>
       </c>
       <c r="AD41" s="13" t="n">
         <v>-0.000171057</v>
       </c>
       <c r="AE41" s="13" t="n">
-        <v>-0.000171057</v>
-      </c>
-      <c r="AF41" s="13" t="n">
         <v>8.66025</v>
       </c>
-      <c r="AH41" s="13" t="n">
+      <c r="AG41" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH41" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI41" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ41" s="13" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
@@ -5103,81 +4949,76 @@
       <c r="I42" s="13" t="n"/>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1021/jacs.5c09249</t>
         </is>
       </c>
       <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="inlineStr">
-        <is>
-          <t>Accelerated Discovery of Energy Transfer-Catalyzed Dearomative Cycloadditions through a Data-Driven Three-Layer Screening Strategy | Journal of the American Chemical Society</t>
-        </is>
+      <c r="M42" s="13" t="n">
+        <v>0.00125442</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.000798267</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.000669974</v>
       </c>
       <c r="P42" s="13" t="n">
-        <v>0.000669974</v>
+        <v>0.00057019</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.00057019</v>
+        <v>0.000456152</v>
       </c>
       <c r="R42" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000470407</v>
       </c>
       <c r="S42" s="13" t="n">
-        <v>0.000470407</v>
+        <v>0.000228076</v>
       </c>
       <c r="T42" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.000285095</v>
       </c>
       <c r="U42" s="13" t="n">
-        <v>0.000285095</v>
+        <v>0.000156802</v>
       </c>
       <c r="V42" s="13" t="n">
         <v>0.000156802</v>
       </c>
       <c r="W42" s="13" t="n">
-        <v>0.000156802</v>
+        <v>1.38778e-18</v>
       </c>
       <c r="X42" s="13" t="n">
-        <v>1.38778e-18</v>
+        <v>7.12738e-05</v>
       </c>
       <c r="Y42" s="13" t="n">
         <v>7.12738e-05</v>
       </c>
       <c r="Z42" s="13" t="n">
-        <v>7.12738e-05</v>
+        <v>-9.97833e-05</v>
       </c>
       <c r="AA42" s="13" t="n">
-        <v>-9.97833e-05</v>
+        <v>-4.27643e-05</v>
       </c>
       <c r="AB42" s="13" t="n">
-        <v>-4.27643e-05</v>
+        <v>2.85095e-05</v>
       </c>
       <c r="AC42" s="13" t="n">
-        <v>2.85095e-05</v>
+        <v>-0.000285095</v>
       </c>
       <c r="AD42" s="13" t="n">
         <v>-0.000285095</v>
       </c>
       <c r="AE42" s="13" t="n">
-        <v>-0.000285095</v>
-      </c>
-      <c r="AF42" s="13" t="n">
         <v>4.7619</v>
       </c>
-      <c r="AH42" s="13" t="n">
+      <c r="AG42" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH42" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI42" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ42" s="13" t="inlineStr">
         <is>
           <t>H5</t>
         </is>
@@ -5212,81 +5053,76 @@
       <c r="I43" s="13" t="n"/>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1002/hlca.200490027</t>
         </is>
       </c>
       <c r="K43" s="13" t="n"/>
-      <c r="L43" s="13" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/epdf/10.1002/hlca.200490027</t>
-        </is>
+      <c r="M43" s="13" t="n">
+        <v>0.00364922</v>
       </c>
       <c r="N43" s="13" t="n">
-        <v>0.00364922</v>
+        <v>0.00353518</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>0.00353518</v>
+        <v>0.00340689</v>
       </c>
       <c r="P43" s="13" t="n">
-        <v>0.00340689</v>
+        <v>0.00342114</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.00342114</v>
+        <v>0.0033071</v>
       </c>
       <c r="R43" s="13" t="n">
-        <v>0.0033071</v>
+        <v>0.00320732</v>
       </c>
       <c r="S43" s="13" t="n">
-        <v>0.00320732</v>
+        <v>0.00319307</v>
       </c>
       <c r="T43" s="13" t="n">
-        <v>0.00319307</v>
+        <v>0.00313605</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>0.00313605</v>
+        <v>0.00323583</v>
       </c>
       <c r="V43" s="13" t="n">
-        <v>0.00323583</v>
+        <v>0.00312179</v>
       </c>
       <c r="W43" s="13" t="n">
-        <v>0.00312179</v>
+        <v>0.00307903</v>
       </c>
       <c r="X43" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.0031503</v>
       </c>
       <c r="Y43" s="13" t="n">
         <v>0.0031503</v>
       </c>
       <c r="Z43" s="13" t="n">
-        <v>0.0031503</v>
+        <v>0.00309328</v>
       </c>
       <c r="AA43" s="13" t="n">
-        <v>0.00309328</v>
+        <v>0.00303626</v>
       </c>
       <c r="AB43" s="13" t="n">
-        <v>0.00303626</v>
+        <v>0.00310754</v>
       </c>
       <c r="AC43" s="13" t="n">
-        <v>0.00310754</v>
+        <v>0.00302201</v>
       </c>
       <c r="AD43" s="13" t="n">
-        <v>0.00302201</v>
+        <v>0.00313605</v>
       </c>
       <c r="AE43" s="13" t="n">
-        <v>0.00313605</v>
-      </c>
-      <c r="AF43" s="13" t="n">
         <v>9.643649999999999</v>
       </c>
-      <c r="AH43" s="13" t="n">
+      <c r="AG43" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH43" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI43" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ43" s="13" t="inlineStr">
         <is>
           <t>A6</t>
         </is>
@@ -5321,81 +5157,76 @@
       <c r="I44" s="13" t="n"/>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L44" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n"/>
+      <c r="M44" s="13" t="n">
+        <v>0.0263428</v>
+      </c>
       <c r="N44" s="13" t="n">
-        <v>0.0263428</v>
+        <v>0.00707036</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>0.00707036</v>
+        <v>0.00409112</v>
       </c>
       <c r="P44" s="13" t="n">
-        <v>0.00409112</v>
+        <v>0.00353518</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.00353518</v>
+        <v>0.00307903</v>
       </c>
       <c r="R44" s="13" t="n">
-        <v>0.00307903</v>
+        <v>0.00275117</v>
       </c>
       <c r="S44" s="13" t="n">
-        <v>0.00275117</v>
+        <v>0.00216672</v>
       </c>
       <c r="T44" s="13" t="n">
-        <v>0.00216672</v>
+        <v>0.00176759</v>
       </c>
       <c r="U44" s="13" t="n">
-        <v>0.00176759</v>
+        <v>0.0016393</v>
       </c>
       <c r="V44" s="13" t="n">
-        <v>0.0016393</v>
+        <v>0.00141122</v>
       </c>
       <c r="W44" s="13" t="n">
-        <v>0.00141122</v>
+        <v>0.0014825</v>
       </c>
       <c r="X44" s="13" t="n">
-        <v>0.0014825</v>
+        <v>0.00121165</v>
       </c>
       <c r="Y44" s="13" t="n">
-        <v>0.00121165</v>
+        <v>0.00132569</v>
       </c>
       <c r="Z44" s="13" t="n">
-        <v>0.00132569</v>
+        <v>0.000812521</v>
       </c>
       <c r="AA44" s="13" t="n">
-        <v>0.000812521</v>
+        <v>0.000755502</v>
       </c>
       <c r="AB44" s="13" t="n">
-        <v>0.000755502</v>
+        <v>0.000712738</v>
       </c>
       <c r="AC44" s="13" t="n">
-        <v>0.000712738</v>
+        <v>0.000513171</v>
       </c>
       <c r="AD44" s="13" t="n">
         <v>0.000513171</v>
       </c>
       <c r="AE44" s="13" t="n">
-        <v>0.000513171</v>
-      </c>
-      <c r="AF44" s="13" t="n">
         <v>6.83967</v>
       </c>
-      <c r="AH44" s="13" t="n">
+      <c r="AG44" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH44" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI44" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ44" s="13" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
@@ -5430,81 +5261,76 @@
       <c r="I45" s="13" t="n"/>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L45" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n"/>
+      <c r="M45" s="13" t="n">
+        <v>0.00125442</v>
+      </c>
       <c r="N45" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.000912305</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.00089805</v>
       </c>
       <c r="P45" s="13" t="n">
-        <v>0.00089805</v>
+        <v>0.000684229</v>
       </c>
       <c r="Q45" s="13" t="n">
         <v>0.000684229</v>
       </c>
       <c r="R45" s="13" t="n">
-        <v>0.000684229</v>
+        <v>0.000470407</v>
       </c>
       <c r="S45" s="13" t="n">
-        <v>0.000470407</v>
+        <v>0.000456152</v>
       </c>
       <c r="T45" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.000399133</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>0.000399133</v>
+        <v>0.000384879</v>
       </c>
       <c r="V45" s="13" t="n">
-        <v>0.000384879</v>
+        <v>0.00027084</v>
       </c>
       <c r="W45" s="13" t="n">
-        <v>0.00027084</v>
+        <v>0.000342114</v>
       </c>
       <c r="X45" s="13" t="n">
-        <v>0.000342114</v>
+        <v>0.00029935</v>
       </c>
       <c r="Y45" s="13" t="n">
         <v>0.00029935</v>
       </c>
       <c r="Z45" s="13" t="n">
-        <v>0.00029935</v>
+        <v>0.000242331</v>
       </c>
       <c r="AA45" s="13" t="n">
-        <v>0.000242331</v>
+        <v>0.000185312</v>
       </c>
       <c r="AB45" s="13" t="n">
-        <v>0.000185312</v>
+        <v>0.000256586</v>
       </c>
       <c r="AC45" s="13" t="n">
-        <v>0.000256586</v>
+        <v>5.7019e-05</v>
       </c>
       <c r="AD45" s="13" t="n">
-        <v>5.7019e-05</v>
+        <v>0.000171057</v>
       </c>
       <c r="AE45" s="13" t="n">
-        <v>0.000171057</v>
-      </c>
-      <c r="AF45" s="13" t="n">
         <v>6.0297</v>
       </c>
-      <c r="AH45" s="13" t="n">
+      <c r="AG45" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH45" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI45" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ45" s="13" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
@@ -5543,81 +5369,76 @@
       <c r="I46" s="13" t="n"/>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L46" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n"/>
+      <c r="M46" s="13" t="n">
+        <v>0.00114038</v>
+      </c>
       <c r="N46" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.000456152</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.00032786</v>
       </c>
       <c r="P46" s="13" t="n">
-        <v>0.00032786</v>
+        <v>0.000228076</v>
       </c>
       <c r="Q46" s="13" t="n">
         <v>0.000228076</v>
       </c>
       <c r="R46" s="13" t="n">
+        <v>0.000128293</v>
+      </c>
+      <c r="S46" s="13" t="n">
         <v>0.000228076</v>
       </c>
-      <c r="S46" s="13" t="n">
-        <v>0.000128293</v>
-      </c>
       <c r="T46" s="13" t="n">
-        <v>0.000228076</v>
+        <v>5.7019e-05</v>
       </c>
       <c r="U46" s="13" t="n">
-        <v>5.7019e-05</v>
+        <v>0.000156802</v>
       </c>
       <c r="V46" s="13" t="n">
         <v>0.000156802</v>
       </c>
       <c r="W46" s="13" t="n">
-        <v>0.000156802</v>
+        <v>1.38778e-18</v>
       </c>
       <c r="X46" s="13" t="n">
-        <v>1.38778e-18</v>
+        <v>7.12738e-05</v>
       </c>
       <c r="Y46" s="13" t="n">
+        <v>0.000185312</v>
+      </c>
+      <c r="Z46" s="13" t="n">
+        <v>-9.97833e-05</v>
+      </c>
+      <c r="AA46" s="13" t="n">
         <v>7.12738e-05</v>
       </c>
-      <c r="Z46" s="13" t="n">
-        <v>0.000185312</v>
-      </c>
-      <c r="AA46" s="13" t="n">
-        <v>-9.97833e-05</v>
-      </c>
       <c r="AB46" s="13" t="n">
-        <v>7.12738e-05</v>
+        <v>-8.55286e-05</v>
       </c>
       <c r="AC46" s="13" t="n">
-        <v>-8.55286e-05</v>
+        <v>-0.000171057</v>
       </c>
       <c r="AD46" s="13" t="n">
-        <v>-0.000171057</v>
+        <v>-5.7019e-05</v>
       </c>
       <c r="AE46" s="13" t="n">
-        <v>-5.7019e-05</v>
-      </c>
-      <c r="AF46" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AH46" s="13" t="n">
+      <c r="AG46" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH46" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI46" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ46" s="13" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
@@ -5652,81 +5473,76 @@
       <c r="I47" s="13" t="n"/>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L47" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n"/>
+      <c r="M47" s="13" t="n">
+        <v>0.00159653</v>
+      </c>
       <c r="N47" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.0014825</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>0.0014825</v>
+        <v>0.0013542</v>
       </c>
       <c r="P47" s="13" t="n">
-        <v>0.0013542</v>
+        <v>0.00136846</v>
       </c>
       <c r="Q47" s="13" t="n">
         <v>0.00136846</v>
       </c>
       <c r="R47" s="13" t="n">
-        <v>0.00136846</v>
+        <v>0.00126867</v>
       </c>
       <c r="S47" s="13" t="n">
-        <v>0.00126867</v>
+        <v>0.00114038</v>
       </c>
       <c r="T47" s="13" t="n">
-        <v>0.00114038</v>
+        <v>0.0011974</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>0.0011974</v>
+        <v>0.00106911</v>
       </c>
       <c r="V47" s="13" t="n">
         <v>0.00106911</v>
       </c>
       <c r="W47" s="13" t="n">
-        <v>0.00106911</v>
+        <v>0.000912305</v>
       </c>
       <c r="X47" s="13" t="n">
-        <v>0.000912305</v>
+        <v>0.0009835790000000001</v>
       </c>
       <c r="Y47" s="13" t="n">
         <v>0.0009835790000000001</v>
       </c>
       <c r="Z47" s="13" t="n">
-        <v>0.0009835790000000001</v>
+        <v>0.000926559</v>
       </c>
       <c r="AA47" s="13" t="n">
-        <v>0.000926559</v>
+        <v>0.00086954</v>
       </c>
       <c r="AB47" s="13" t="n">
-        <v>0.00086954</v>
+        <v>0.000826776</v>
       </c>
       <c r="AC47" s="13" t="n">
-        <v>0.000826776</v>
+        <v>0.000627209</v>
       </c>
       <c r="AD47" s="13" t="n">
-        <v>0.000627209</v>
+        <v>0.000741248</v>
       </c>
       <c r="AE47" s="13" t="n">
-        <v>0.000741248</v>
-      </c>
-      <c r="AF47" s="13" t="n">
         <v>5.58851</v>
       </c>
-      <c r="AH47" s="13" t="n">
+      <c r="AG47" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH47" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI47" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ47" s="13" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
@@ -5761,85 +5577,80 @@
       <c r="I48" s="13" t="n"/>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>CV measured by MJK</t>
-        </is>
-      </c>
-      <c r="L48" s="13" t="inlineStr">
-        <is>
-          <t>Cyclic Bifunctional Reagents Enabling a Strain-Release-Driven Formal [3 + 2] Cycloaddition of 2H-Azirines by Cascade Energy Transfer | Journal of the American Chemical Society</t>
-        </is>
+          <t>measured by MJK; also reported in https://doi.org/10.1021/jacs.4c18080</t>
+        </is>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>0.00490364</v>
       </c>
       <c r="N48" s="13" t="n">
-        <v>0.00490364</v>
+        <v>0.00353518</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>0.00353518</v>
+        <v>0.00260862</v>
       </c>
       <c r="P48" s="13" t="n">
-        <v>0.00260862</v>
+        <v>0.00228076</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.00228076</v>
+        <v>0.00159653</v>
       </c>
       <c r="R48" s="13" t="n">
-        <v>0.00159653</v>
+        <v>0.00115464</v>
       </c>
       <c r="S48" s="13" t="n">
-        <v>0.00115464</v>
+        <v>0.000684229</v>
       </c>
       <c r="T48" s="13" t="n">
-        <v>0.000684229</v>
+        <v>0.000399133</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>0.000399133</v>
+        <v>0.000498917</v>
       </c>
       <c r="V48" s="13" t="n">
-        <v>0.000498917</v>
+        <v>0.00027084</v>
       </c>
       <c r="W48" s="13" t="n">
-        <v>0.00027084</v>
+        <v>0.000228076</v>
       </c>
       <c r="X48" s="13" t="n">
-        <v>0.000228076</v>
+        <v>0.000185312</v>
       </c>
       <c r="Y48" s="13" t="n">
         <v>0.000185312</v>
       </c>
       <c r="Z48" s="13" t="n">
-        <v>0.000185312</v>
+        <v>-9.97833e-05</v>
       </c>
       <c r="AA48" s="13" t="n">
-        <v>-9.97833e-05</v>
+        <v>-4.27643e-05</v>
       </c>
       <c r="AB48" s="13" t="n">
-        <v>-4.27643e-05</v>
+        <v>-0.000199567</v>
       </c>
       <c r="AC48" s="13" t="n">
-        <v>-0.000199567</v>
+        <v>-0.000171057</v>
       </c>
       <c r="AD48" s="13" t="n">
         <v>-0.000171057</v>
       </c>
       <c r="AE48" s="13" t="n">
-        <v>-0.000171057</v>
-      </c>
-      <c r="AF48" s="13" t="n">
         <v>4.54545</v>
       </c>
-      <c r="AH48" s="13" t="n">
+      <c r="AG48" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH48" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI48" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ48" s="13" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
@@ -5872,81 +5683,76 @@
       <c r="I49" s="13" t="n"/>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>https://doi.org/10.1021/jacs.2c05687</t>
         </is>
       </c>
       <c r="K49" s="13" t="n"/>
-      <c r="L49" s="13" t="inlineStr">
-        <is>
-          <t>Visible-Light Photocatalyzed peri-(3 + 2) Cycloadditions of Quinolines | Journal of the American Chemical Society</t>
-        </is>
+      <c r="M49" s="13" t="n">
+        <v>0.0161934</v>
       </c>
       <c r="N49" s="13" t="n">
-        <v>0.0161934</v>
+        <v>0.0110617</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>0.0110617</v>
+        <v>0.00739822</v>
       </c>
       <c r="P49" s="13" t="n">
-        <v>0.00739822</v>
+        <v>0.00604402</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.00604402</v>
+        <v>0.00410537</v>
       </c>
       <c r="R49" s="13" t="n">
-        <v>0.00410537</v>
+        <v>0.00309328</v>
       </c>
       <c r="S49" s="13" t="n">
-        <v>0.00309328</v>
+        <v>0.00171057</v>
       </c>
       <c r="T49" s="13" t="n">
-        <v>0.00171057</v>
+        <v>0.0011974</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>0.0011974</v>
+        <v>0.000955069</v>
       </c>
       <c r="V49" s="13" t="n">
         <v>0.000955069</v>
       </c>
       <c r="W49" s="13" t="n">
-        <v>0.000955069</v>
+        <v>0.000798267</v>
       </c>
       <c r="X49" s="13" t="n">
-        <v>0.000798267</v>
+        <v>0.000755502</v>
       </c>
       <c r="Y49" s="13" t="n">
-        <v>0.000755502</v>
+        <v>0.000641464</v>
       </c>
       <c r="Z49" s="13" t="n">
-        <v>0.000641464</v>
+        <v>1.42548e-05</v>
       </c>
       <c r="AA49" s="13" t="n">
-        <v>1.42548e-05</v>
+        <v>7.12738e-05</v>
       </c>
       <c r="AB49" s="13" t="n">
-        <v>7.12738e-05</v>
+        <v>-8.55286e-05</v>
       </c>
       <c r="AC49" s="13" t="n">
-        <v>-8.55286e-05</v>
+        <v>-5.7019e-05</v>
       </c>
       <c r="AD49" s="13" t="n">
         <v>-5.7019e-05</v>
       </c>
       <c r="AE49" s="13" t="n">
-        <v>-5.7019e-05</v>
-      </c>
-      <c r="AF49" s="13" t="n">
         <v>2.83943</v>
       </c>
-      <c r="AH49" s="13" t="n">
+      <c r="AG49" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH49" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI49" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ49" s="13" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
@@ -5985,81 +5791,76 @@
       <c r="I50" s="13" t="n"/>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>CV measured</t>
-        </is>
-      </c>
-      <c r="L50" s="13" t="n"/>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n"/>
+      <c r="M50" s="13" t="n">
+        <v>0.00125442</v>
+      </c>
       <c r="N50" s="13" t="n">
-        <v>0.00125442</v>
+        <v>0.000456152</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>0.000456152</v>
+        <v>0.00032786</v>
       </c>
       <c r="P50" s="13" t="n">
-        <v>0.00032786</v>
+        <v>0.000342114</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.000342114</v>
+        <v>0.000114038</v>
       </c>
       <c r="R50" s="13" t="n">
-        <v>0.000114038</v>
+        <v>0.000242331</v>
       </c>
       <c r="S50" s="13" t="n">
-        <v>0.000242331</v>
+        <v>0</v>
       </c>
       <c r="T50" s="13" t="n">
-        <v>0</v>
+        <v>-5.7019e-05</v>
       </c>
       <c r="U50" s="13" t="n">
-        <v>-5.7019e-05</v>
+        <v>-7.12738e-05</v>
       </c>
       <c r="V50" s="13" t="n">
         <v>-7.12738e-05</v>
       </c>
       <c r="W50" s="13" t="n">
-        <v>-7.12738e-05</v>
+        <v>-0.000114038</v>
       </c>
       <c r="X50" s="13" t="n">
-        <v>-0.000114038</v>
+        <v>-0.000156802</v>
       </c>
       <c r="Y50" s="13" t="n">
+        <v>-4.27643e-05</v>
+      </c>
+      <c r="Z50" s="13" t="n">
+        <v>-0.000213821</v>
+      </c>
+      <c r="AA50" s="13" t="n">
         <v>-0.000156802</v>
       </c>
-      <c r="Z50" s="13" t="n">
-        <v>-4.27643e-05</v>
-      </c>
-      <c r="AA50" s="13" t="n">
-        <v>-0.000213821</v>
-      </c>
       <c r="AB50" s="13" t="n">
-        <v>-0.000156802</v>
+        <v>-0.000199567</v>
       </c>
       <c r="AC50" s="13" t="n">
-        <v>-0.000199567</v>
+        <v>-0.000285095</v>
       </c>
       <c r="AD50" s="13" t="n">
-        <v>-0.000285095</v>
+        <v>-0.000171057</v>
       </c>
       <c r="AE50" s="13" t="n">
-        <v>-0.000171057</v>
-      </c>
-      <c r="AF50" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AH50" s="13" t="n">
+      <c r="AG50" s="13" t="n">
         <v>5</v>
       </c>
+      <c r="AH50" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="AI50" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AJ50" s="13" t="inlineStr">
         <is>
           <t>H6</t>
         </is>
@@ -6067,10 +5868,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="M1:AE1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="N1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="F1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6082,7 +5883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6319,18 +6120,18 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>redox_source_type</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>measured (CV in this lab), literature, estimated, or unattributed.</t>
+          <t>CV: measured in this lab. Otherwise the DOI of the paper the potentials were taken from, or 'estimated' where neither exists.</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: redox_source_type</t>
+          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: redox_source</t>
         </is>
       </c>
     </row>
@@ -6342,41 +6143,45 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>redox_source_note</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr"/>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Free-text provenance from the lab record.</t>
+          <t>From the lab record: solvent, conversion, who measured, caveats.</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: redox_source_note</t>
+          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: redox_comment</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Molar extinction coefficients in MeCN / mM-1 cm-1</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>redox_doi</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr"/>
+          <t>epsilon_380 / mM-1 cm-1</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>mM-1 cm-1</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Literature source, where given.</t>
+          <t>Molar extinction coefficient at 380 nm.</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: redox_doi</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_380_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6193,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>epsilon_380 / mM-1 cm-1</t>
+          <t>epsilon_390 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -6398,12 +6203,12 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 380 nm.</t>
+          <t>Molar extinction coefficient at 390 nm.</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_380_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_390_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6220,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>epsilon_390 / mM-1 cm-1</t>
+          <t>epsilon_400 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -6425,12 +6230,12 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 390 nm.</t>
+          <t>Molar extinction coefficient at 400 nm.</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_390_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_400_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6247,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>epsilon_400 / mM-1 cm-1</t>
+          <t>epsilon_405 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -6452,12 +6257,12 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 400 nm.</t>
+          <t>Molar extinction coefficient at 405 nm.</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_400_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_405_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6274,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>epsilon_405 / mM-1 cm-1</t>
+          <t>epsilon_415 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -6479,12 +6284,12 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 405 nm.</t>
+          <t>Molar extinction coefficient at 415 nm.</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_405_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_415_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6301,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>epsilon_415 / mM-1 cm-1</t>
+          <t>epsilon_425 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -6506,12 +6311,12 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 415 nm.</t>
+          <t>Molar extinction coefficient at 425 nm.</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_415_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_425_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6328,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>epsilon_425 / mM-1 cm-1</t>
+          <t>epsilon_450 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -6533,12 +6338,12 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 425 nm.</t>
+          <t>Molar extinction coefficient at 450 nm.</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_425_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_450_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6355,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>epsilon_450 / mM-1 cm-1</t>
+          <t>epsilon_475 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -6560,12 +6365,12 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 450 nm.</t>
+          <t>Molar extinction coefficient at 475 nm.</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_450_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_475_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6382,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>epsilon_475 / mM-1 cm-1</t>
+          <t>epsilon_490 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -6587,12 +6392,12 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 475 nm.</t>
+          <t>Molar extinction coefficient at 490 nm.</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_475_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_490_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6409,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>epsilon_490 / mM-1 cm-1</t>
+          <t>epsilon_495 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -6614,12 +6419,12 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 490 nm.</t>
+          <t>Molar extinction coefficient at 495 nm.</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_490_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_495_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6436,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>epsilon_495 / mM-1 cm-1</t>
+          <t>epsilon_500 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -6641,12 +6446,12 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 495 nm.</t>
+          <t>Molar extinction coefficient at 500 nm.</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_495_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_500_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6463,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>epsilon_500 / mM-1 cm-1</t>
+          <t>epsilon_510 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -6668,12 +6473,12 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 500 nm.</t>
+          <t>Molar extinction coefficient at 510 nm.</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_500_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_510_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6490,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>epsilon_510 / mM-1 cm-1</t>
+          <t>epsilon_520 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -6695,12 +6500,12 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 510 nm.</t>
+          <t>Molar extinction coefficient at 520 nm.</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_510_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_520_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6517,7 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>epsilon_520 / mM-1 cm-1</t>
+          <t>epsilon_580 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -6722,12 +6527,12 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 520 nm.</t>
+          <t>Molar extinction coefficient at 580 nm.</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_520_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_580_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6544,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>epsilon_580 / mM-1 cm-1</t>
+          <t>epsilon_590 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -6749,12 +6554,12 @@
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 580 nm.</t>
+          <t>Molar extinction coefficient at 590 nm.</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_580_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_590_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6571,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>epsilon_590 / mM-1 cm-1</t>
+          <t>epsilon_600 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -6776,12 +6581,12 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 590 nm.</t>
+          <t>Molar extinction coefficient at 600 nm.</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_590_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_600_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6598,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>epsilon_600 / mM-1 cm-1</t>
+          <t>epsilon_625 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -6803,12 +6608,12 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 600 nm.</t>
+          <t>Molar extinction coefficient at 625 nm.</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_600_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_625_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6625,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>epsilon_625 / mM-1 cm-1</t>
+          <t>epsilon_645 / mM-1 cm-1</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -6830,12 +6635,12 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 625 nm.</t>
+          <t>Molar extinction coefficient at 645 nm.</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_625_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_645_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6847,49 +6652,49 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>epsilon_645 / mM-1 cm-1</t>
+          <t>max_read_rsd / %</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>mM-1 cm-1</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Molar extinction coefficient at 645 nm.</t>
+          <t>Largest relative spread between repeat reads across the 18 wavelengths.</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_645_mM-1cm-1</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: max_read_rsd_percent</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Molar extinction coefficients in MeCN / mM-1 cm-1</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>max_read_rsd / %</t>
+          <t>c_stock / mM</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>mM</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Largest relative spread between repeat reads across the 18 wavelengths.</t>
+          <t>Stock concentration.</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: max_read_rsd_percent</t>
+          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: c_stock_mM</t>
         </is>
       </c>
     </row>
@@ -6901,22 +6706,18 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>c_stock / mM</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>mM</t>
-        </is>
-      </c>
+          <t>deck_position</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr"/>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Stock concentration.</t>
+          <t>Deck slot of the stock plate.</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: c_stock_mM</t>
+          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: deck_position</t>
         </is>
       </c>
     </row>
@@ -6928,46 +6729,34 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>deck_position</t>
+          <t>well_position</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr"/>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Deck slot of the stock plate.</t>
+          <t>Well of the stock plate.</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: deck_position</t>
+          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: well_position</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>well_position</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr"/>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>Well of the stock plate.</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: well_position</t>
-        </is>
-      </c>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="n"/>
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>One row per quencher. The potentials are the recorded ones. The cyclic voltammetry</t>
+        </is>
+      </c>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="16" t="n"/>
@@ -6976,7 +6765,7 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>One row per quencher. The potentials are the recorded ones. The cyclic voltammetry</t>
+          <t>traces deposited for 19 quenchers, and the potentials re-read from them as a check,</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
@@ -6987,7 +6776,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>traces deposited for 19 quenchers, and the potentials re-read from them as a check,</t>
+          <t>are in experimental_data_raw/quencher_cyclic_voltammetry/.</t>
         </is>
       </c>
       <c r="B37" s="15" t="n"/>
@@ -6998,7 +6787,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>are in experimental_data_raw/quencher_cyclic_voltammetry/.</t>
+          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
@@ -7006,17 +6795,6 @@
       <c r="D38" s="16" t="n"/>
       <c r="E38" s="15" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="15" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -489,7 +489,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="2" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>6-Me-quinoline</t>
+          <t>6-methylquinoline</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>2-Nitro-m-Xylene</t>
+          <t>1,3-dimethyl-2-nitrobenzene</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Benzothiophene</t>
+          <t>benzo[b]thiophene</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Quinoxaline</t>
+          <t>quinoxaline</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Isoquinoline</t>
+          <t>isoquinoline</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Coumarin</t>
+          <t>coumarin</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>OiPr bifunc</t>
+          <t>benzophenone O-(isopropoxycarbonyl) oxime</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>2-Ph-3-Me-Thiazol</t>
+          <t>3-methyl-2-phenylthiophene</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Diphenyldisulfide</t>
+          <t>diphenyl disulfide</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Dibenzyldisulfide</t>
+          <t>dibenzyl disulfide</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>dihydro azaborinine</t>
+          <t>1,2-dihydro-1,2-benzazaborinine</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>maleimide</t>
+          <t>N-methylmaleimide</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Butyl-Methacrylate</t>
+          <t>butyl methacrylate</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Inden</t>
+          <t>indene</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>5-Me-Pyridone</t>
+          <t>5-methylpyridin-2(1H)-one</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>(BnSe)2</t>
+          <t>dibenzyl diselenide</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>oxadiazole</t>
+          <t>5,5-dimethyl-3-phenyl-4,5-dihydro-1,2,4-oxadiazole</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>sulfur bifunc</t>
+          <t>benzophenone O-[(benzylsulfanyl)carbonyl] oxime</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Ethylphenylpropiolat</t>
+          <t>ethyl 3-phenylpropiolate</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>4-Oxo-Quinazolin</t>
+          <t>4-oxo-2-phenylquinazolin-3(4H)-yl 3-phenylpropanoate</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Bpin-Benzothiophen</t>
+          <t>2-(benzo[b]thiophen-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Bpin-Benzofuran</t>
+          <t>2-(benzofuran-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Br-Benzothiophen</t>
+          <t>2-bromobenzo[b]thiophene</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Br-Benzofuran</t>
+          <t>2-bromobenzofuran</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Di-Br-Thiophene</t>
+          <t>2,5-dibromothiophene</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Benzoyl-Thiazol</t>
+          <t>2-benzoylthiazole</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Isoxazolon</t>
+          <t>4,4-dimethyl-3-phenylisoxazol-5(4H)-one</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>E-Stilbene</t>
+          <t>(E)-stilbene</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>N-Peroxide</t>
+          <t>6-phenyl-5-oxa-6-azaspiro[2.4]heptane-4,7-dione</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>Thioamide 1</t>
+          <t>1-(thiobenzoyl)pyrrolidine</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Thioamide 2</t>
+          <t>N-methyl-N-phenylpropanethioamide</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>oxime ether</t>
+          <t>(Z)-3,4-dihydronaphthalen-1(2H)-one O-methyl oxime</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Z-Stilbene</t>
+          <t>(Z)-stilbene</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>Ac-Pyrol</t>
+          <t>2-acetyl-1-methylpyrrole</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>F-styrene</t>
+          <t>1-bromo-4-(2,2-difluorovinyl)benzene</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>butadiene</t>
+          <t>1,3-butadiene</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>4-Me-2-Ph-Thiazol</t>
+          <t>4-methyl-2-phenylthiazole</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>Ph-Oxazol</t>
+          <t>2-phenyloxazole</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>alpha-Methylstyrol</t>
+          <t>alpha-methylstyrene</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>2-Benzoyl-Furan</t>
+          <t>2-benzoylfuran</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>2-Acetyl-4-Me-Thiophen</t>
+          <t>2-acetyl-4-methylthiophene</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>2-Acetylpyridine</t>
+          <t>2-acetylpyridine</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>vinyl selenoxide</t>
+          <t>phenyl vinyl selenoxide</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>Azirin-Intermediat</t>
+          <t>2,2-dimethyl-3-phenyl-2H-azirine</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>Quinolin-8-Ester</t>
+          <t>methyl quinoline-8-carboxylate</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Cyclohexenone</t>
+          <t>cyclohex-2-en-1-one</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
@@ -5980,7 +5980,7 @@
       <c r="C4" s="15" t="inlineStr"/>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Compound, as recorded.</t>
+          <t>Name derived from the SMILES (checked by name-to-structure conversion).</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI50"/>
+  <dimension ref="A1:AH50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,6 @@
     <col width="2" customWidth="1" min="32" max="32"/>
     <col width="14" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
-    <col width="15" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -535,7 +534,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Redox potentials / V vs SCE</t>
         </is>
       </c>
       <c r="G1" s="4" t="n"/>
@@ -572,7 +571,6 @@
         </is>
       </c>
       <c r="AH1" s="8" t="n"/>
-      <c r="AI1" s="8" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -726,11 +724,6 @@
         </is>
       </c>
       <c r="AH2" s="12" t="inlineStr">
-        <is>
-          <t>deck_position</t>
-        </is>
-      </c>
-      <c r="AI2" s="12" t="inlineStr">
         <is>
           <t>well_position</t>
         </is>
@@ -778,7 +771,7 @@
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>measured by PPR</t>
+          <t>measured by PPR; voltammogram not in the data</t>
         </is>
       </c>
       <c r="M3" s="13" t="n">
@@ -842,11 +835,6 @@
         <v>5</v>
       </c>
       <c r="AH3" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI3" s="13" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -950,11 +938,6 @@
         <v>5</v>
       </c>
       <c r="AH4" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI4" s="13" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
@@ -1057,11 +1040,6 @@
       </c>
       <c r="AH5" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI5" s="13" t="inlineStr">
-        <is>
           <t>C1</t>
         </is>
       </c>
@@ -1164,11 +1142,6 @@
         <v>5</v>
       </c>
       <c r="AH6" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI6" s="13" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
@@ -1267,11 +1240,6 @@
       </c>
       <c r="AH7" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI7" s="13" t="inlineStr">
-        <is>
           <t>E1</t>
         </is>
       </c>
@@ -1369,11 +1337,6 @@
       </c>
       <c r="AH8" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI8" s="13" t="inlineStr">
-        <is>
           <t>F1</t>
         </is>
       </c>
@@ -1481,11 +1444,6 @@
       </c>
       <c r="AH9" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI9" s="13" t="inlineStr">
-        <is>
           <t>G1</t>
         </is>
       </c>
@@ -1593,11 +1551,6 @@
       </c>
       <c r="AH10" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI10" s="13" t="inlineStr">
-        <is>
           <t>H1</t>
         </is>
       </c>
@@ -1622,17 +1575,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1.403</v>
+        <v>1.487</v>
       </c>
       <c r="G11" s="13" t="n"/>
       <c r="H11" s="13" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+        <v>-2.396</v>
+      </c>
+      <c r="I11" s="13" t="n"/>
       <c r="J11" s="13" t="inlineStr">
         <is>
           <t>CV</t>
@@ -1640,7 +1589,7 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>no lab record; consistent with the deposited voltammogram (009)</t>
+          <t>E_Ox: onset; E_Red: onset</t>
         </is>
       </c>
       <c r="M11" s="13" t="n">
@@ -1704,11 +1653,6 @@
         <v>5</v>
       </c>
       <c r="AH11" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI11" s="13" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
@@ -1813,11 +1757,6 @@
       </c>
       <c r="AH12" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI12" s="13" t="inlineStr">
-        <is>
           <t>B2</t>
         </is>
       </c>
@@ -1921,11 +1860,6 @@
       </c>
       <c r="AH13" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI13" s="13" t="inlineStr">
-        <is>
           <t>C2</t>
         </is>
       </c>
@@ -1950,11 +1884,11 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1.401</v>
+        <v>1.436</v>
       </c>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1966,7 +1900,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K14" s="13" t="n"/>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: no reduction wave inside the window</t>
+        </is>
+      </c>
       <c r="M14" s="13" t="n">
         <v>0.00296499</v>
       </c>
@@ -2028,11 +1966,6 @@
         <v>5</v>
       </c>
       <c r="AH14" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI14" s="13" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
@@ -2131,11 +2064,6 @@
       </c>
       <c r="AH15" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI15" s="13" t="inlineStr">
-        <is>
           <t>E2</t>
         </is>
       </c>
@@ -2233,11 +2161,6 @@
       </c>
       <c r="AH16" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI16" s="13" t="inlineStr">
-        <is>
           <t>F2</t>
         </is>
       </c>
@@ -2339,11 +2262,6 @@
       </c>
       <c r="AH17" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI17" s="13" t="inlineStr">
-        <is>
           <t>G2</t>
         </is>
       </c>
@@ -2386,7 +2304,7 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>measured by NHO/PAU</t>
+          <t>measured by NHO/PAU; voltammogram not in the data</t>
         </is>
       </c>
       <c r="M18" s="13" t="n">
@@ -2450,11 +2368,6 @@
         <v>5</v>
       </c>
       <c r="AH18" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI18" s="13" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
@@ -2480,11 +2393,11 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1.2</v>
+        <v>1.252</v>
       </c>
       <c r="G19" s="13" t="n"/>
       <c r="H19" s="13" t="n">
-        <v>-0.2</v>
+        <v>-1.568</v>
       </c>
       <c r="I19" s="13" t="n"/>
       <c r="J19" s="13" t="inlineStr">
@@ -2494,7 +2407,7 @@
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>poor-quality voltammogram</t>
+          <t>E_Ox: onset; E_Red: onset</t>
         </is>
       </c>
       <c r="M19" s="13" t="n">
@@ -2558,11 +2471,6 @@
         <v>5</v>
       </c>
       <c r="AH19" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI19" s="13" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
@@ -2588,11 +2496,11 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.86</v>
+        <v>0.908</v>
       </c>
       <c r="G20" s="13" t="n"/>
       <c r="H20" s="13" t="n">
-        <v>-2.18</v>
+        <v>-2.155</v>
       </c>
       <c r="I20" s="13" t="n"/>
       <c r="J20" s="13" t="inlineStr">
@@ -2600,7 +2508,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K20" s="13" t="n"/>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M20" s="13" t="n">
         <v>0.00205269</v>
       </c>
@@ -2662,11 +2574,6 @@
         <v>5</v>
       </c>
       <c r="AH20" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI20" s="13" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
@@ -2775,11 +2682,6 @@
       </c>
       <c r="AH21" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI21" s="13" t="inlineStr">
-        <is>
           <t>C3</t>
         </is>
       </c>
@@ -2882,11 +2784,6 @@
           <t>D3</t>
         </is>
       </c>
-      <c r="AI22" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n">
@@ -2908,11 +2805,11 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>2</v>
+        <v>2.017</v>
       </c>
       <c r="G23" s="13" t="n"/>
       <c r="H23" s="13" t="n">
-        <v>-1.8</v>
+        <v>-1.792</v>
       </c>
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="13" t="inlineStr">
@@ -2920,7 +2817,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K23" s="13" t="n"/>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M23" s="13" t="n">
         <v>0.00125442</v>
       </c>
@@ -2982,11 +2883,6 @@
         <v>5</v>
       </c>
       <c r="AH23" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI23" s="13" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
@@ -3016,7 +2912,7 @@
       </c>
       <c r="G24" s="13" t="n"/>
       <c r="H24" s="13" t="n">
-        <v>-1.55</v>
+        <v>-1.436</v>
       </c>
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="13" t="inlineStr">
@@ -3024,7 +2920,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K24" s="13" t="n"/>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: the lab's reading of its voltammogram, which the two deposited repeats cannot confirm (onset +2.19 V, and a +0.34 V feature in the second run only); E_Red: onset</t>
+        </is>
+      </c>
       <c r="M24" s="13" t="n">
         <v>0.00307903</v>
       </c>
@@ -3086,11 +2986,6 @@
         <v>5</v>
       </c>
       <c r="AH24" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI24" s="13" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
@@ -3116,11 +3011,11 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>1.84</v>
+        <v>1.687</v>
       </c>
       <c r="G25" s="13" t="n"/>
       <c r="H25" s="13" t="n">
-        <v>-2.2</v>
+        <v>-2.162</v>
       </c>
       <c r="I25" s="13" t="n"/>
       <c r="J25" s="13" t="inlineStr">
@@ -3128,7 +3023,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K25" s="13" t="n"/>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M25" s="13" t="n">
         <v>0.00193865</v>
       </c>
@@ -3190,11 +3089,6 @@
         <v>5</v>
       </c>
       <c r="AH25" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI25" s="13" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
@@ -3220,11 +3114,11 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>1.86</v>
+        <v>1.895</v>
       </c>
       <c r="G26" s="13" t="n"/>
       <c r="H26" s="13" t="n">
-        <v>-2.3</v>
+        <v>-2.318</v>
       </c>
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="13" t="inlineStr">
@@ -3232,7 +3126,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K26" s="13" t="n"/>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M26" s="13" t="n">
         <v>0.00342114</v>
       </c>
@@ -3294,11 +3192,6 @@
         <v>5</v>
       </c>
       <c r="AH26" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI26" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
@@ -3338,7 +3231,7 @@
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>measured by TJS</t>
+          <t>measured by TJS; voltammogram not in the data</t>
         </is>
       </c>
       <c r="M27" s="13" t="n">
@@ -3402,11 +3295,6 @@
         <v>5</v>
       </c>
       <c r="AH27" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI27" s="13" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
@@ -3450,7 +3338,7 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>measured by TJS</t>
+          <t>measured by TJS; voltammogram not in the data</t>
         </is>
       </c>
       <c r="M28" s="13" t="n">
@@ -3514,11 +3402,6 @@
         <v>5</v>
       </c>
       <c r="AH28" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI28" s="13" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
@@ -3544,11 +3427,11 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1.84</v>
+        <v>1.911</v>
       </c>
       <c r="G29" s="13" t="n"/>
       <c r="H29" s="13" t="n">
-        <v>-2</v>
+        <v>-1.951</v>
       </c>
       <c r="I29" s="13" t="n"/>
       <c r="J29" s="13" t="inlineStr">
@@ -3556,7 +3439,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K29" s="13" t="n"/>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M29" s="13" t="n">
         <v>0.00296499</v>
       </c>
@@ -3618,11 +3505,6 @@
         <v>5</v>
       </c>
       <c r="AH29" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI29" s="13" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
@@ -3656,7 +3538,7 @@
         </is>
       </c>
       <c r="H30" s="13" t="n">
-        <v>-1.25</v>
+        <v>-1.225</v>
       </c>
       <c r="I30" s="13" t="n"/>
       <c r="J30" s="13" t="inlineStr">
@@ -3664,7 +3546,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K30" s="13" t="n"/>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: no oxidation wave inside the window; E_Red: half-wave</t>
+        </is>
+      </c>
       <c r="M30" s="13" t="n">
         <v>0.104003</v>
       </c>
@@ -3726,11 +3612,6 @@
         <v>5</v>
       </c>
       <c r="AH30" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI30" s="13" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
@@ -3835,11 +3716,6 @@
       </c>
       <c r="AH31" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI31" s="13" t="inlineStr">
-        <is>
           <t>E4</t>
         </is>
       </c>
@@ -3939,11 +3815,6 @@
       </c>
       <c r="AH32" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI32" s="13" t="inlineStr">
-        <is>
           <t>F4</t>
         </is>
       </c>
@@ -3990,7 +3861,7 @@
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>measured by NHO</t>
+          <t>measured by NHO; voltammogram not in the data</t>
         </is>
       </c>
       <c r="M33" s="13" t="n">
@@ -4054,11 +3925,6 @@
         <v>5</v>
       </c>
       <c r="AH33" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI33" s="13" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
@@ -4167,11 +4033,6 @@
       </c>
       <c r="AH34" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI34" s="13" t="inlineStr">
-        <is>
           <t>H4</t>
         </is>
       </c>
@@ -4279,11 +4140,6 @@
       </c>
       <c r="AH35" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI35" s="13" t="inlineStr">
-        <is>
           <t>A5</t>
         </is>
       </c>
@@ -4308,11 +4164,11 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>1.8</v>
+        <v>1.798</v>
       </c>
       <c r="G36" s="13" t="n"/>
       <c r="H36" s="13" t="n">
-        <v>-2.2</v>
+        <v>-2.255</v>
       </c>
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="13" t="inlineStr">
@@ -4320,7 +4176,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K36" s="13" t="n"/>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M36" s="13" t="n">
         <v>0.00114038</v>
       </c>
@@ -4382,11 +4242,6 @@
         <v>5</v>
       </c>
       <c r="AH36" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI36" s="13" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
@@ -4487,11 +4342,6 @@
       </c>
       <c r="AH37" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI37" s="13" t="inlineStr">
-        <is>
           <t>C5</t>
         </is>
       </c>
@@ -4516,11 +4366,11 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="G38" s="13" t="n"/>
       <c r="H38" s="13" t="n">
-        <v>-2.2</v>
+        <v>-2.212</v>
       </c>
       <c r="I38" s="13" t="n"/>
       <c r="J38" s="13" t="inlineStr">
@@ -4528,7 +4378,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K38" s="13" t="n"/>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M38" s="13" t="n">
         <v>0.000912305</v>
       </c>
@@ -4590,11 +4444,6 @@
         <v>5</v>
       </c>
       <c r="AH38" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI38" s="13" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
@@ -4620,11 +4469,11 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="G39" s="13" t="n"/>
       <c r="H39" s="13" t="n">
-        <v>-2.2</v>
+        <v>-2.288</v>
       </c>
       <c r="I39" s="13" t="n"/>
       <c r="J39" s="13" t="inlineStr">
@@ -4632,7 +4481,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K39" s="13" t="n"/>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M39" s="13" t="n">
         <v>0.0172198</v>
       </c>
@@ -4694,11 +4547,6 @@
         <v>5</v>
       </c>
       <c r="AH39" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI39" s="13" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
@@ -4807,11 +4655,6 @@
       </c>
       <c r="AH40" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI40" s="13" t="inlineStr">
-        <is>
           <t>F5</t>
         </is>
       </c>
@@ -4836,11 +4679,11 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>1.6</v>
+        <v>1.675</v>
       </c>
       <c r="G41" s="13" t="n"/>
       <c r="H41" s="13" t="n">
-        <v>-2.05</v>
+        <v>-2.1</v>
       </c>
       <c r="I41" s="13" t="n"/>
       <c r="J41" s="13" t="inlineStr">
@@ -4848,7 +4691,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K41" s="13" t="n"/>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: half-wave</t>
+        </is>
+      </c>
       <c r="M41" s="13" t="n">
         <v>0.00376326</v>
       </c>
@@ -4910,11 +4757,6 @@
         <v>5</v>
       </c>
       <c r="AH41" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI41" s="13" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
@@ -5015,11 +4857,6 @@
       </c>
       <c r="AH42" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI42" s="13" t="inlineStr">
-        <is>
           <t>H5</t>
         </is>
       </c>
@@ -5119,11 +4956,6 @@
       </c>
       <c r="AH43" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI43" s="13" t="inlineStr">
-        <is>
           <t>A6</t>
         </is>
       </c>
@@ -5148,11 +4980,11 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>2.1</v>
+        <v>2.189</v>
       </c>
       <c r="G44" s="13" t="n"/>
       <c r="H44" s="13" t="n">
-        <v>-1.65</v>
+        <v>-1.6</v>
       </c>
       <c r="I44" s="13" t="n"/>
       <c r="J44" s="13" t="inlineStr">
@@ -5160,7 +4992,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K44" s="13" t="n"/>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: half-wave</t>
+        </is>
+      </c>
       <c r="M44" s="13" t="n">
         <v>0.0263428</v>
       </c>
@@ -5222,11 +5058,6 @@
         <v>5</v>
       </c>
       <c r="AH44" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI44" s="13" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
@@ -5252,11 +5083,11 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>1.94</v>
+        <v>2.017</v>
       </c>
       <c r="G45" s="13" t="n"/>
       <c r="H45" s="13" t="n">
-        <v>-1.75</v>
+        <v>-1.698</v>
       </c>
       <c r="I45" s="13" t="n"/>
       <c r="J45" s="13" t="inlineStr">
@@ -5264,7 +5095,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K45" s="13" t="n"/>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: onset; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M45" s="13" t="n">
         <v>0.00125442</v>
       </c>
@@ -5326,11 +5161,6 @@
         <v>5</v>
       </c>
       <c r="AH45" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI45" s="13" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
@@ -5356,7 +5186,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -5364,7 +5194,7 @@
         </is>
       </c>
       <c r="H46" s="13" t="n">
-        <v>-1.75</v>
+        <v>-1.736</v>
       </c>
       <c r="I46" s="13" t="n"/>
       <c r="J46" s="13" t="inlineStr">
@@ -5372,7 +5202,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K46" s="13" t="n"/>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: no oxidation wave inside the window; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M46" s="13" t="n">
         <v>0.00114038</v>
       </c>
@@ -5434,11 +5268,6 @@
         <v>5</v>
       </c>
       <c r="AH46" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI46" s="13" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
@@ -5476,7 +5305,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K47" s="13" t="n"/>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>voltammogram not in the data</t>
+        </is>
+      </c>
       <c r="M47" s="13" t="n">
         <v>0.00159653</v>
       </c>
@@ -5538,11 +5371,6 @@
         <v>5</v>
       </c>
       <c r="AH47" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI47" s="13" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
@@ -5568,11 +5396,11 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1.9</v>
+        <v>1.884</v>
       </c>
       <c r="G48" s="13" t="n"/>
       <c r="H48" s="13" t="n">
-        <v>-2</v>
+        <v>-2.291</v>
       </c>
       <c r="I48" s="13" t="n"/>
       <c r="J48" s="13" t="inlineStr">
@@ -5582,7 +5410,7 @@
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>measured by MJK; also reported in https://doi.org/10.1021/jacs.4c18080</t>
+          <t>E_Ox: onset; E_Red: onset</t>
         </is>
       </c>
       <c r="M48" s="13" t="n">
@@ -5646,11 +5474,6 @@
         <v>5</v>
       </c>
       <c r="AH48" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI48" s="13" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
@@ -5749,11 +5572,6 @@
       </c>
       <c r="AH49" s="13" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI49" s="13" t="inlineStr">
-        <is>
           <t>G6</t>
         </is>
       </c>
@@ -5778,7 +5596,7 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -5786,7 +5604,7 @@
         </is>
       </c>
       <c r="H50" s="13" t="n">
-        <v>-1.95</v>
+        <v>-1.965</v>
       </c>
       <c r="I50" s="13" t="n"/>
       <c r="J50" s="13" t="inlineStr">
@@ -5794,7 +5612,11 @@
           <t>CV</t>
         </is>
       </c>
-      <c r="K50" s="13" t="n"/>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: no oxidation wave inside the window; E_Red: onset</t>
+        </is>
+      </c>
       <c r="M50" s="13" t="n">
         <v>0.00125442</v>
       </c>
@@ -5856,11 +5678,6 @@
         <v>5</v>
       </c>
       <c r="AH50" s="13" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="AI50" s="13" t="inlineStr">
         <is>
           <t>H6</t>
         </is>
@@ -5870,7 +5687,7 @@
   <mergeCells count="4">
     <mergeCell ref="M1:AE1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AG1:AH1"/>
     <mergeCell ref="F1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5883,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5939,7 +5756,7 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: quencher_id</t>
+          <t>compound_identification.xlsx: Quenchers/quencher_id</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5779,7 @@
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: quencher_name</t>
+          <t>compound_identification.xlsx: Quenchers/quencher_id</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5802,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: name</t>
+          <t>compound_identification.xlsx: Quenchers/name</t>
         </is>
       </c>
     </row>
@@ -6008,14 +5825,14 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: smiles</t>
+          <t>compound_identification.xlsx: Quenchers/smiles</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Redox potentials / V vs SCE</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -6035,14 +5852,14 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: E_Ox_vs_SCE_exp</t>
+          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Ox_vs_SCE_V</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Redox potentials / V vs SCE</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -6058,14 +5875,14 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: E_Ox_bound</t>
+          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Ox_bound</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Redox potentials / V vs SCE</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -6085,14 +5902,14 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: E_Red_vs_SCE_exp</t>
+          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Red_vs_SCE_V</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Redox potentials / V vs SCE</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -6108,14 +5925,14 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: E_Red_bound</t>
+          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Red_bound</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Redox potentials / V vs SCE</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -6131,14 +5948,14 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: redox_source</t>
+          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: source</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Redox potentials, as recorded / V vs SCE</t>
+          <t>Redox potentials / V vs SCE</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -6149,12 +5966,12 @@
       <c r="C11" s="15" t="inlineStr"/>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>From the lab record: solvent, conversion, who measured, caveats.</t>
+          <t>For a deposited voltammogram, which descriptor was read (onset, half-wave, or no wave inside the window); otherwise from the literature record.</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: redox_comment</t>
+          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: comment</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6511,7 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: c_stock_mM</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: c_stock_mM</t>
         </is>
       </c>
     </row>
@@ -6706,46 +6523,34 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>deck_position</t>
+          <t>well_position</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr"/>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Deck slot of the stock plate.</t>
+          <t>Well of the stock plate.</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: deck_position</t>
+          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: well</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>well_position</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr"/>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>Well of the stock plate.</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: well_position</t>
-        </is>
-      </c>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n"/>
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>One row per quencher. The potentials are read from the voltammogram for the 19</t>
+        </is>
+      </c>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="15" t="n"/>
       <c r="D34" s="16" t="n"/>
@@ -6754,7 +6559,7 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>One row per quencher. The potentials are the recorded ones. The cyclic voltammetry</t>
+          <t>quenchers that have one, and taken from the literature for the others; both are in</t>
         </is>
       </c>
       <c r="B35" s="15" t="n"/>
@@ -6765,7 +6570,7 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>traces deposited for 19 quenchers, and the potentials re-read from them as a check,</t>
+          <t>experimental_data_raw/quencher_cyclic_voltammetry/.</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
@@ -6776,7 +6581,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>are in experimental_data_raw/quencher_cyclic_voltammetry/.</t>
+          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
       <c r="B37" s="15" t="n"/>
@@ -6784,17 +6589,6 @@
       <c r="D37" s="16" t="n"/>
       <c r="E37" s="15" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="15" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -2612,12 +2612,12 @@
       <c r="I21" s="13" t="n"/>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>https://doi.org/10.1021/acscatal.5c01142</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>no source recorded (lab record: 'ask RET')</t>
+          <t>E_Red: first of two irreversible reductions, -2.15 V vs Fc+/Fc = -1.69 V vs SCE (the second -2.29 V = -1.83 V); E_Ox: bound not attributed</t>
         </is>
       </c>
       <c r="M21" s="13" t="n">

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -5797,7 +5797,7 @@
       <c r="C4" s="15" t="inlineStr"/>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Name derived from the SMILES (checked by name-to-structure conversion).</t>
+          <t>Name derived from the SMILES.</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Oxidation potential. Where E_Ox_bound is set, a limit, not a value.</t>
+          <t>Oxidation potential, or a limit where E_Ox_bound is set.</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -5870,7 +5870,7 @@
       <c r="C7" s="15" t="inlineStr"/>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>'&gt;': not oxidized within the window; the true value lies above the one given. Blank: a value.</t>
+          <t>'&gt;': no oxidation within the window, the potential lies above the value given. Blank: a measured value.</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Reduction potential. Where E_Red_bound is set, a limit, not a value.</t>
+          <t>Reduction potential, or a limit where E_Red_bound is set.</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5920,7 +5920,7 @@
       <c r="C9" s="15" t="inlineStr"/>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>'&lt;': not reduced within the window; the true value lies below the one given. Blank: a value.</t>
+          <t>'&lt;': no reduction within the window, the potential lies below the value given. Blank: a measured value.</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5943,7 +5943,7 @@
       <c r="C10" s="15" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>CV: measured in this lab. Otherwise the DOI of the paper the potentials were taken from, or 'estimated' where neither exists.</t>
+          <t>CV: measured in this lab. Otherwise the DOI of the literature source, or 'estimated'.</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -5966,7 +5966,7 @@
       <c r="C11" s="15" t="inlineStr"/>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>For a deposited voltammogram, which descriptor was read (onset, half-wave, or no wave inside the window); otherwise from the literature record.</t>
+          <t>For a measured voltammogram, the value read (onset, half-wave, or no wave inside the window); otherwise the note from the literature file.</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -5966,7 +5966,7 @@
       <c r="C11" s="15" t="inlineStr"/>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>For a measured voltammogram, the value read (onset, half-wave, or no wave inside the window); otherwise the note from the literature file.</t>
+          <t>Free-text note from quencher_redox_measured.csv or quencher_redox_literature.csv.</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -6548,7 +6548,7 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>One row per quencher. The potentials are read from the voltammogram for the 19</t>
+          <t>One row per quencher. The potentials are read by hand from the voltammograms or</t>
         </is>
       </c>
       <c r="B34" s="15" t="n"/>
@@ -6559,7 +6559,7 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>quenchers that have one, and taken from the literature for the others; both are in</t>
+          <t>taken from the literature, and entered in quencher_redox_measured.csv or</t>
         </is>
       </c>
       <c r="B35" s="15" t="n"/>
@@ -6570,7 +6570,7 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_cyclic_voltammetry/.</t>
+          <t>quencher_redox_literature.csv in experimental_data_raw/quencher_cyclic_voltammetry/.</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -766,14 +766,10 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>measured by PPR; voltammogram not in the data</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1038/s41929-026-01566-z</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="n"/>
       <c r="M3" s="13" t="n">
         <v>0.0038773</v>
       </c>
@@ -962,8 +958,14 @@
           <t>CC1=C(C(=CC=C1)C)[N+](=O)[O-]</t>
         </is>
       </c>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
+      <c r="F5" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
       <c r="H5" s="13" t="n">
         <v>-1.407</v>
       </c>
@@ -975,7 +977,7 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>converted from Fc/Fc+ to SCE</t>
+          <t>E_Red: converted from Fc/Fc+ to SCE; E_Ox: edge of the window</t>
         </is>
       </c>
       <c r="M5" s="13" t="n">
@@ -1166,8 +1168,14 @@
           <t>C12=NC=CN=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
+      <c r="F7" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
       <c r="H7" s="13" t="n">
         <v>-1.8</v>
       </c>
@@ -1177,7 +1185,11 @@
           <t>https://doi.org/10.1039/j19680000381</t>
         </is>
       </c>
-      <c r="K7" s="13" t="n"/>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: edge of the window</t>
+        </is>
+      </c>
       <c r="M7" s="13" t="n">
         <v>0.0226936</v>
       </c>
@@ -1263,8 +1275,14 @@
           <t>C12=CN=CC=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
+      <c r="F8" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
       <c r="H8" s="13" t="n">
         <v>-2.2</v>
       </c>
@@ -1274,7 +1292,11 @@
           <t>https://doi.org/10.1039/j19680000381</t>
         </is>
       </c>
-      <c r="K8" s="13" t="n"/>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: edge of the window</t>
+        </is>
+      </c>
       <c r="M8" s="13" t="n">
         <v>0.0102634</v>
       </c>
@@ -1575,11 +1597,11 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1.487</v>
+        <v>1.4</v>
       </c>
       <c r="G11" s="13" t="n"/>
       <c r="H11" s="13" t="n">
-        <v>-2.396</v>
+        <v>-2.4</v>
       </c>
       <c r="I11" s="13" t="n"/>
       <c r="J11" s="13" t="inlineStr">
@@ -1884,7 +1906,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1.436</v>
+        <v>1.35</v>
       </c>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n">
@@ -1990,8 +2012,14 @@
           <t>O=C1C=CC(N1C)=O</t>
         </is>
       </c>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
+      <c r="F15" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
       <c r="H15" s="13" t="n">
         <v>-0.95</v>
       </c>
@@ -2001,7 +2029,11 @@
           <t>https://doi.org/10.1016/S0040-4039(00)01248-X</t>
         </is>
       </c>
-      <c r="K15" s="13" t="n"/>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: edge of the window</t>
+        </is>
+      </c>
       <c r="M15" s="13" t="n">
         <v>0.0047896</v>
       </c>
@@ -2087,8 +2119,14 @@
           <t>CC(C(OCCCC)=O)=C</t>
         </is>
       </c>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
+      <c r="F16" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
       <c r="H16" s="13" t="n">
         <v>-2.41</v>
       </c>
@@ -2098,7 +2136,11 @@
           <t>https://doi.org/10.1246/bcsj.51.339</t>
         </is>
       </c>
-      <c r="K16" s="13" t="n"/>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: edge of the window</t>
+        </is>
+      </c>
       <c r="M16" s="13" t="n">
         <v>0.00216672</v>
       </c>
@@ -2188,8 +2230,14 @@
         <v>1.72</v>
       </c>
       <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
+      <c r="H17" s="13" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
           <t>https://doi.org/10.1038/s41929-023-01089-x</t>
@@ -2197,7 +2245,7 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>reduction potential not reported</t>
+          <t>E_Red: not reported; edge of the window</t>
         </is>
       </c>
       <c r="M17" s="13" t="n">
@@ -2299,14 +2347,10 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>measured by NHO/PAU; voltammogram not in the data</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.1002/anie.9565676</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n"/>
       <c r="M18" s="13" t="n">
         <v>0.00410537</v>
       </c>
@@ -2393,11 +2437,11 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1.252</v>
+        <v>1.25</v>
       </c>
       <c r="G19" s="13" t="n"/>
       <c r="H19" s="13" t="n">
-        <v>-1.568</v>
+        <v>-1.6</v>
       </c>
       <c r="I19" s="13" t="n"/>
       <c r="J19" s="13" t="inlineStr">
@@ -2496,11 +2540,11 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.908</v>
+        <v>0.85</v>
       </c>
       <c r="G20" s="13" t="n"/>
       <c r="H20" s="13" t="n">
-        <v>-2.155</v>
+        <v>-2.15</v>
       </c>
       <c r="I20" s="13" t="n"/>
       <c r="J20" s="13" t="inlineStr">
@@ -2805,11 +2849,11 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>2.017</v>
+        <v>1.95</v>
       </c>
       <c r="G23" s="13" t="n"/>
       <c r="H23" s="13" t="n">
-        <v>-1.792</v>
+        <v>-1.8</v>
       </c>
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="13" t="inlineStr">
@@ -2912,7 +2956,7 @@
       </c>
       <c r="G24" s="13" t="n"/>
       <c r="H24" s="13" t="n">
-        <v>-1.436</v>
+        <v>-1.4</v>
       </c>
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="13" t="inlineStr">
@@ -3011,11 +3055,11 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>1.687</v>
+        <v>1.65</v>
       </c>
       <c r="G25" s="13" t="n"/>
       <c r="H25" s="13" t="n">
-        <v>-2.162</v>
+        <v>-2.15</v>
       </c>
       <c r="I25" s="13" t="n"/>
       <c r="J25" s="13" t="inlineStr">
@@ -3114,11 +3158,11 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>1.895</v>
+        <v>1.85</v>
       </c>
       <c r="G26" s="13" t="n"/>
       <c r="H26" s="13" t="n">
-        <v>-2.318</v>
+        <v>-2.3</v>
       </c>
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="13" t="inlineStr">
@@ -3427,11 +3471,11 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1.911</v>
+        <v>1.85</v>
       </c>
       <c r="G29" s="13" t="n"/>
       <c r="H29" s="13" t="n">
-        <v>-1.951</v>
+        <v>-1.95</v>
       </c>
       <c r="I29" s="13" t="n"/>
       <c r="J29" s="13" t="inlineStr">
@@ -3538,7 +3582,7 @@
         </is>
       </c>
       <c r="H30" s="13" t="n">
-        <v>-1.225</v>
+        <v>-1.15</v>
       </c>
       <c r="I30" s="13" t="n"/>
       <c r="J30" s="13" t="inlineStr">
@@ -3968,7 +4012,7 @@
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>estimated from Leandro's thioamides; no reference recorded</t>
+          <t>estimated from structurally related thioamides</t>
         </is>
       </c>
       <c r="M34" s="13" t="n">
@@ -4075,7 +4119,7 @@
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>estimated from Leandro's thioamides; no reference recorded</t>
+          <t>estimated from structurally related thioamides</t>
         </is>
       </c>
       <c r="M35" s="13" t="n">
@@ -4164,11 +4208,11 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>1.798</v>
+        <v>1.75</v>
       </c>
       <c r="G36" s="13" t="n"/>
       <c r="H36" s="13" t="n">
-        <v>-2.255</v>
+        <v>-2.25</v>
       </c>
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="13" t="inlineStr">
@@ -4366,11 +4410,11 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="G38" s="13" t="n"/>
       <c r="H38" s="13" t="n">
-        <v>-2.212</v>
+        <v>-2.3</v>
       </c>
       <c r="I38" s="13" t="n"/>
       <c r="J38" s="13" t="inlineStr">
@@ -4469,11 +4513,11 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="G39" s="13" t="n"/>
       <c r="H39" s="13" t="n">
-        <v>-2.288</v>
+        <v>-2.3</v>
       </c>
       <c r="I39" s="13" t="n"/>
       <c r="J39" s="13" t="inlineStr">
@@ -4679,11 +4723,11 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>1.675</v>
+        <v>1.6</v>
       </c>
       <c r="G41" s="13" t="n"/>
       <c r="H41" s="13" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="I41" s="13" t="n"/>
       <c r="J41" s="13" t="inlineStr">
@@ -4980,11 +5024,11 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>2.189</v>
+        <v>2.2</v>
       </c>
       <c r="G44" s="13" t="n"/>
       <c r="H44" s="13" t="n">
-        <v>-1.6</v>
+        <v>-1.55</v>
       </c>
       <c r="I44" s="13" t="n"/>
       <c r="J44" s="13" t="inlineStr">
@@ -5083,11 +5127,11 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>2.017</v>
+        <v>1.95</v>
       </c>
       <c r="G45" s="13" t="n"/>
       <c r="H45" s="13" t="n">
-        <v>-1.698</v>
+        <v>-1.7</v>
       </c>
       <c r="I45" s="13" t="n"/>
       <c r="J45" s="13" t="inlineStr">
@@ -5194,7 +5238,7 @@
         </is>
       </c>
       <c r="H46" s="13" t="n">
-        <v>-1.736</v>
+        <v>-1.65</v>
       </c>
       <c r="I46" s="13" t="n"/>
       <c r="J46" s="13" t="inlineStr">
@@ -5396,11 +5440,11 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1.884</v>
+        <v>1.55</v>
       </c>
       <c r="G48" s="13" t="n"/>
       <c r="H48" s="13" t="n">
-        <v>-2.291</v>
+        <v>-2.3</v>
       </c>
       <c r="I48" s="13" t="n"/>
       <c r="J48" s="13" t="inlineStr">
@@ -5498,8 +5542,14 @@
           <t>O=C(C1=CC=CC2=CC=CN=C21)OC</t>
         </is>
       </c>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
+      <c r="F49" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
       <c r="H49" s="13" t="n">
         <v>-1.87</v>
       </c>
@@ -5509,7 +5559,11 @@
           <t>https://doi.org/10.1021/jacs.2c05687</t>
         </is>
       </c>
-      <c r="K49" s="13" t="n"/>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>E_Ox: edge of the window</t>
+        </is>
+      </c>
       <c r="M49" s="13" t="n">
         <v>0.0161934</v>
       </c>
@@ -5604,7 +5658,7 @@
         </is>
       </c>
       <c r="H50" s="13" t="n">
-        <v>-1.965</v>
+        <v>-2</v>
       </c>
       <c r="I50" s="13" t="n"/>
       <c r="J50" s="13" t="inlineStr">

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="H5" s="13" t="n">
-        <v>-1.407</v>
+        <v>-1.41</v>
       </c>
       <c r="I5" s="13" t="n"/>
       <c r="J5" s="13" t="inlineStr">

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -1498,17 +1498,17 @@
         </is>
       </c>
       <c r="H10" s="13" t="n">
-        <v>-2.37</v>
+        <v>-1.92</v>
       </c>
       <c r="I10" s="13" t="n"/>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41557-022-01008-w</t>
+          <t>https://doi.org/10.1038/s41557-022-01008-w; https://doi.org/10.1038/s41929-020-00553-2</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>estimated: the value is for the analog with Me instead of iPr</t>
+          <t>estimated: the value is for the analog with Me instead of iPr; E_Red from the second source (compound 2h): -2.37 V vs Fc+/Fc in DMF = -1.92 V vs SCE, conversion +0.45 V as given there</t>
         </is>
       </c>
       <c r="M10" s="13" t="n">

--- a/data/experimental_data_processed/quencher_properties_exp.xlsx
+++ b/data/experimental_data_processed/quencher_properties_exp.xlsx
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Ox_vs_SCE_V</t>
+          <t>experimental_data_processed/quencher_redox_potentials.csv: E_Ox_vs_SCE_V</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Ox_bound</t>
+          <t>experimental_data_processed/quencher_redox_potentials.csv: E_Ox_bound</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Red_vs_SCE_V</t>
+          <t>experimental_data_processed/quencher_redox_potentials.csv: E_Red_vs_SCE_V</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: E_Red_bound</t>
+          <t>experimental_data_processed/quencher_redox_potentials.csv: E_Red_bound</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: source</t>
+          <t>experimental_data_processed/quencher_redox_potentials.csv: source</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_cyclic_voltammetry/quencher_redox_potentials.csv: comment</t>
+          <t>experimental_data_processed/quencher_redox_potentials.csv: comment</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_380_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_380_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_390_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_390_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_400_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_400_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_405_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_405_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_415_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_415_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_425_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_425_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_450_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_450_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_475_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_475_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_490_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_490_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_495_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_495_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_500_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_500_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_510_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_510_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_520_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_520_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_580_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_580_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_590_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_590_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_600_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_600_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_625_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_625_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: epsilon_645_mM-1cm-1</t>
+          <t>experimental_data_processed/absorption_extinction.csv: epsilon_645_mM-1cm-1</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: max_read_rsd_percent</t>
+          <t>experimental_data_processed/absorption_extinction.csv: max_read_rsd_percent</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: c_stock_mM</t>
+          <t>experimental_data_processed/absorption_extinction.csv: c_stock_mM</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>experimental_data_raw/quencher_absorption/absorption_extinction.csv: well</t>
+          <t>experimental_data_processed/absorption_extinction.csv: well</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>quencher_redox_literature.csv in experimental_data_raw/quencher_cyclic_voltammetry/.</t>
+          <t>quencher_redox_literature.csv in experimental_data_processed/.</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
